--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,12 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88172B05-BE62-4EC5-856F-8B26C56C219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029DDA5-1006-487A-BF27-0EBDCC949AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Arrhythmia" sheetId="2" r:id="rId2"/>
+    <sheet name="Parkinson" sheetId="3" r:id="rId3"/>
+    <sheet name="Shuttle" sheetId="4" r:id="rId4"/>
+    <sheet name="WBC" sheetId="5" r:id="rId5"/>
+    <sheet name="SpamBase" sheetId="6" r:id="rId6"/>
+    <sheet name="WPBC" sheetId="7" r:id="rId7"/>
+    <sheet name="HeartDisease" sheetId="8" r:id="rId8"/>
+    <sheet name="Glass" sheetId="9" r:id="rId9"/>
+    <sheet name="Hep" sheetId="10" r:id="rId10"/>
+    <sheet name="Pima" sheetId="11" r:id="rId11"/>
+    <sheet name="PenDigits" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="40">
   <si>
     <t>Arrhy</t>
   </si>
@@ -146,6 +157,39 @@
   </si>
   <si>
     <t>Gamma AUC</t>
+  </si>
+  <si>
+    <t>Algorithm</t>
+  </si>
+  <si>
+    <t>ROC AUC</t>
+  </si>
+  <si>
+    <t>KNNW</t>
+  </si>
+  <si>
+    <t>LOF</t>
+  </si>
+  <si>
+    <t>SimplifiedLOF</t>
+  </si>
+  <si>
+    <t>LoOP</t>
+  </si>
+  <si>
+    <t>ODIN</t>
+  </si>
+  <si>
+    <t>KDEOS</t>
+  </si>
+  <si>
+    <t>INFLO</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Average/Count</t>
   </si>
 </sst>
 </file>
@@ -492,10 +536,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="3" width="15.140625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" hidden="1" customWidth="1"/>
@@ -506,9 +550,12 @@
     <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -548,8 +595,41 @@
       <c r="M1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -580,7 +660,7 @@
         <v>9.0814897342029743E-3</v>
       </c>
       <c r="J2" s="3">
-        <f>G2-M2</f>
+        <f t="shared" ref="J2:J12" si="0">G2-M2</f>
         <v>9.0814897342029743E-3</v>
       </c>
       <c r="K2" t="s">
@@ -593,7 +673,7 @@
         <v>0.752</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -610,7 +690,7 @@
         <v>0.88660000000000005</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F12" si="0">B3-L3</f>
+        <f t="shared" ref="F3:F12" si="1">B3-L3</f>
         <v>6.9654195011336961E-2</v>
       </c>
       <c r="G3" s="3">
@@ -620,11 +700,11 @@
         <v>0.85409999999999997</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I12" si="1">G3-L3</f>
+        <f t="shared" ref="I3:I12" si="2">G3-L3</f>
         <v>6.816609977324195E-2</v>
       </c>
       <c r="J3" s="3">
-        <f>G3-M3</f>
+        <f t="shared" si="0"/>
         <v>8.5816099773242005E-2</v>
       </c>
       <c r="K3" t="s">
@@ -637,7 +717,7 @@
         <v>0.65234999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -651,7 +731,7 @@
         <v>0.82015384615384601</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.9246153846159686E-3</v>
       </c>
       <c r="G4" s="3">
@@ -661,11 +741,11 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.7386153846153949E-2</v>
       </c>
       <c r="J4" s="3">
-        <f>G4-M4</f>
+        <f t="shared" si="0"/>
         <v>2.5338461538459978E-3</v>
       </c>
       <c r="K4" t="s">
@@ -678,7 +758,7 @@
         <v>0.81762000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -692,7 +772,7 @@
         <v>0.99859154929577398</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-4.6917370892020083E-3</v>
       </c>
       <c r="G5" s="3">
@@ -702,11 +782,11 @@
         <v>0.98670000000000002</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4115492957740283E-3</v>
       </c>
       <c r="J5" s="3">
-        <f>G5-M5</f>
+        <f t="shared" si="0"/>
         <v>1.4115492957740283E-3</v>
       </c>
       <c r="K5" t="s">
@@ -719,7 +799,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -730,7 +810,7 @@
         <v>0.88929999999999998</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.7279367654042974E-2</v>
       </c>
       <c r="G6" s="3">
@@ -740,11 +820,11 @@
         <v>0.92220000000000002</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.6539471053443942E-2</v>
       </c>
       <c r="J6" s="3">
-        <f>G6-M6</f>
+        <f t="shared" si="0"/>
         <v>7.6539471053443942E-2</v>
       </c>
       <c r="K6" t="s">
@@ -757,7 +837,7 @@
         <v>0.57347000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -768,7 +848,7 @@
         <v>0.95530000000000004</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5.3541389319430976E-2</v>
       </c>
       <c r="G7" s="3">
@@ -778,11 +858,11 @@
         <v>0.98599999999999999</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.1357367901931017E-2</v>
       </c>
       <c r="J7" s="3">
-        <f>G7-M7</f>
+        <f t="shared" si="0"/>
         <v>-9.3373679019310707E-3</v>
       </c>
       <c r="K7" t="s">
@@ -795,7 +875,7 @@
         <v>0.54090000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -806,7 +886,7 @@
         <v>0.99519999999999997</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-5.6781111111110949E-2</v>
       </c>
       <c r="G8" s="3">
@@ -816,11 +896,11 @@
         <v>0.99390000000000001</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.5503333333333904E-2</v>
       </c>
       <c r="J8" s="3">
-        <f>G8-M8</f>
+        <f t="shared" si="0"/>
         <v>1.6336666666666E-2</v>
       </c>
       <c r="K8" t="s">
@@ -833,7 +913,7 @@
         <v>0.68383000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -844,7 +924,7 @@
         <v>0.8196</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-2.6284227642277003E-2</v>
       </c>
       <c r="G9" s="3">
@@ -854,11 +934,11 @@
         <v>0.93869999999999998</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.3032195121951982E-2</v>
       </c>
       <c r="J9" s="3">
-        <f>G9-M9</f>
+        <f t="shared" si="0"/>
         <v>5.6878048780479862E-3</v>
       </c>
       <c r="K9" t="s">
@@ -871,7 +951,7 @@
         <v>0.87480000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -882,7 +962,7 @@
         <v>0.96850000000000003</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-4.3625752009184948E-2</v>
       </c>
       <c r="G10" s="3">
@@ -892,11 +972,11 @@
         <v>0.93610000000000004</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.4199804822043998E-2</v>
       </c>
       <c r="J10" s="3">
-        <f>G10-M10</f>
+        <f t="shared" si="0"/>
         <v>-1.149804822044076E-3</v>
       </c>
       <c r="K10" t="s">
@@ -909,7 +989,7 @@
         <v>0.78588000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -920,7 +1000,7 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-2.554134328358304E-2</v>
       </c>
       <c r="G11" s="3">
@@ -930,11 +1010,11 @@
         <v>0.997</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.4895820895523002E-2</v>
       </c>
       <c r="J11" s="3">
-        <f>G11-M11</f>
+        <f t="shared" si="0"/>
         <v>3.6741791044769823E-3</v>
       </c>
       <c r="K11" t="s">
@@ -947,7 +1027,7 @@
         <v>0.73224</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -958,7 +1038,7 @@
         <v>0.97070000000000001</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-9.7250974817230107E-3</v>
       </c>
       <c r="G12" s="3">
@@ -968,11 +1048,11 @@
         <v>0.97860000000000003</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.5143948009750456E-3</v>
       </c>
       <c r="J12" s="3">
-        <f>G12-M12</f>
+        <f t="shared" si="0"/>
         <v>-9.5143948009750456E-3</v>
       </c>
       <c r="K12" t="s">
@@ -985,7 +1065,10 @@
         <v>0.99212</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
       <c r="B13">
         <f>AVERAGE(B2:B12)</f>
         <v>0.78172770812943915</v>
@@ -1021,6 +1104,50 @@
       <c r="M13" s="2">
         <f>AVERAGE(M2:M12)</f>
         <v>0.76385363636363646</v>
+      </c>
+      <c r="N13">
+        <f>AVERAGE(Arrhythmia!D8,Parkinson!C6,Shuttle!C5,WBC!C4,SpamBase!C6,WPBC!C4,HeartDisease!C6,Glass!C5,Hep!C5,Pima!C6,PenDigits!C5)</f>
+        <v>0.74898363636363641</v>
+      </c>
+      <c r="O13">
+        <f>AVERAGE(Arrhythmia!D12,Parkinson!C7,Shuttle!C7,WBC!C7,SpamBase!C9,WPBC!C8,HeartDisease!C9,Glass!C7,Hep!C8,Pima!C10,PenDigits!C9)</f>
+        <v>0.73779636363636358</v>
+      </c>
+      <c r="P13">
+        <f>AVERAGE(Arrhythmia!D16,Parkinson!C11,Shuttle!C11,WBC!C10,SpamBase!C12,WPBC!C11,HeartDisease!C11,Glass!C10,Hep!C11,Pima!C12,PenDigits!C13)</f>
+        <v>0.71585272727272731</v>
+      </c>
+      <c r="Q13">
+        <f>AVERAGE(Arrhythmia!D20,Parkinson!C14,Shuttle!C14,WBC!C12,SpamBase!C14,WPBC!C14,HeartDisease!C14,Glass!C12,Hep!C15,Pima!C14,PenDigits!C16)</f>
+        <v>0.7080581818181817</v>
+      </c>
+      <c r="R13">
+        <f>AVERAGE(Arrhythmia!D23,Parkinson!C18,Shuttle!C18,WBC!C15,SpamBase!C16,WPBC!C17,HeartDisease!C18,Glass!C15,Hep!C19,Pima!C16,PenDigits!C20)</f>
+        <v>0.68091363636363633</v>
+      </c>
+      <c r="S13">
+        <f>AVERAGE(Arrhythmia!D25,Parkinson!C21,Shuttle!C22,WBC!C18,SpamBase!C20,WPBC!C19,HeartDisease!C21,Glass!C18,Hep!C22,Pima!C20,PenDigits!C24)</f>
+        <v>0.70191727272727278</v>
+      </c>
+      <c r="T13">
+        <f>AVERAGE(Arrhythmia!D28,Parkinson!C24,Shuttle!C25,WBC!C21,SpamBase!C24,WPBC!C21,HeartDisease!C25,Glass!C22,Hep!C26,Pima!C21,PenDigits!C27)</f>
+        <v>0.70524545454545462</v>
+      </c>
+      <c r="U13">
+        <f>AVERAGE(Arrhythmia!D30,Parkinson!C28,Shuttle!C28,WBC!C24,SpamBase!C26,WPBC!C24,HeartDisease!C28,Glass!C25,Hep!C29,Pima!C24,PenDigits!C30)</f>
+        <v>0.63380727272727266</v>
+      </c>
+      <c r="V13">
+        <f>AVERAGE(Arrhythmia!D33,Parkinson!C32,Shuttle!C32,WBC!C28,SpamBase!C30,WPBC!C27,HeartDisease!C32,Glass!C28,Hep!C32,Pima!C26,PenDigits!C34)</f>
+        <v>0.75610909090909084</v>
+      </c>
+      <c r="W13">
+        <f>AVERAGE(Arrhythmia!D36,Parkinson!C35,Shuttle!C36,WBC!C31,SpamBase!C34,WPBC!C30,HeartDisease!C36,Glass!C32,Hep!C36,Pima!C29,PenDigits!C37)</f>
+        <v>0.69330909090909087</v>
+      </c>
+      <c r="X13">
+        <f>AVERAGE(Arrhythmia!D39,Parkinson!C39,Shuttle!C39,WBC!C32,SpamBase!C37,WPBC!C33,HeartDisease!C40,Glass!C35,Hep!C39,Pima!C32,PenDigits!C41)</f>
+        <v>0.74376999999999993</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -1032,4 +1159,4099 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEBCE60-A305-4996-8394-EDFED30DAA67}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.78588000000000002</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B4)</f>
+        <v>0.78588000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.77842</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.77612000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.69116</v>
+      </c>
+      <c r="C5">
+        <f>MAX(B5:B7)</f>
+        <v>0.74856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.74856</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.74168000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.76693</v>
+      </c>
+      <c r="C8">
+        <f>MAX(B8:B10)</f>
+        <v>0.80367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.80023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.80367</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.72789999999999999</v>
+      </c>
+      <c r="C11">
+        <f>MAX(B11:B14)</f>
+        <v>0.73823000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.73363999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.73823000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14">
+        <v>0.73823000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.69230999999999998</v>
+      </c>
+      <c r="C15">
+        <f>MAX(B15:B18)</f>
+        <v>0.72331000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.72331000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>0.70665999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>0.72272999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.67393999999999998</v>
+      </c>
+      <c r="C19">
+        <f>MAX(B19:B21)</f>
+        <v>0.73823000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.71641999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>0.73823000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0.71584000000000003</v>
+      </c>
+      <c r="C22">
+        <f>MAX(B22:B25)</f>
+        <v>0.74970999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>0.74339999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>0.74455000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>0.74970999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>0.59126999999999996</v>
+      </c>
+      <c r="C26">
+        <f>MAX(B26:B28)</f>
+        <v>0.70952999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>0.70952999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>0.70838000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>0.44890999999999998</v>
+      </c>
+      <c r="C29">
+        <f>MAX(B29:B31)</f>
+        <v>0.71182999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.70608000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.71182999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.78759999999999997</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B35)</f>
+        <v>0.82892999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.78415999999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.82892999999999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>0.78874999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.56486999999999998</v>
+      </c>
+      <c r="C36">
+        <f>MAX(B36:B38)</f>
+        <v>0.60275999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.53156999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.60275999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>0.81745000000000001</v>
+      </c>
+      <c r="C39">
+        <f>MAX(B39:B42)</f>
+        <v>0.82721</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.79564000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.82203999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.82721</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8693EBA-F9E5-4205-8DE2-5CF3643D9239}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.73109999999999997</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B5)</f>
+        <v>0.73224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.73224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.73192999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.73187000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.71123000000000003</v>
+      </c>
+      <c r="C6">
+        <f>MAX(B6:B9)</f>
+        <v>0.72943999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.71386000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.72921000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>0.72943999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.68449000000000004</v>
+      </c>
+      <c r="C10">
+        <f>MAX(B10:B11)</f>
+        <v>0.68955</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>0.68955</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.62085000000000001</v>
+      </c>
+      <c r="C12">
+        <f>MAX(B12:B13)</f>
+        <v>0.62131000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.62131000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.58389000000000002</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B15)</f>
+        <v>0.60921999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.60921999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.56013999999999997</v>
+      </c>
+      <c r="C16">
+        <f>MAX(B16:B19)</f>
+        <v>0.57003999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.56925000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.56938</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.57003999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.63636999999999999</v>
+      </c>
+      <c r="C20">
+        <f>MAX(B20)</f>
+        <v>0.63636999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>0.74827999999999995</v>
+      </c>
+      <c r="C21">
+        <f>MAX(B21:B23)</f>
+        <v>0.76080999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.75512999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>0.76080999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>0.55620999999999998</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B25)</f>
+        <v>0.55620999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>0.53607000000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <v>0.72306000000000004</v>
+      </c>
+      <c r="C26">
+        <f>MAX(B26:B28)</f>
+        <v>0.72887999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>0.72567999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>0.72887999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>0.61728000000000005</v>
+      </c>
+      <c r="C29">
+        <f>MAX(B29:B31)</f>
+        <v>0.61728000000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>0.61375000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>0.61621999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32">
+        <v>0.68786000000000003</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B34)</f>
+        <v>0.70121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>0.69167999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>0.70121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5377EC-BA22-47EB-98DB-A8ABB998676D}">
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.98255999999999999</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B4)</f>
+        <v>0.99212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.99212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.99175999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.92906</v>
+      </c>
+      <c r="C5">
+        <f>MAX(B5:B8)</f>
+        <v>0.99160000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.99160000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.99158000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.99150000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.56969999999999998</v>
+      </c>
+      <c r="C9">
+        <f>MAX(B9:B12)</f>
+        <v>0.96580999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.59387999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>0.96469000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12">
+        <v>0.96580999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.53820999999999997</v>
+      </c>
+      <c r="C13">
+        <f>MAX(B13:B15)</f>
+        <v>0.96679999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14">
+        <v>0.96197999999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>0.96679999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.54798999999999998</v>
+      </c>
+      <c r="C16">
+        <f>MAX(B16:B19)</f>
+        <v>0.96231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>0.55501</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>0.96167000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>0.96231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.58098000000000005</v>
+      </c>
+      <c r="C20">
+        <f>MAX(B20:B23)</f>
+        <v>0.75034000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>0.58501000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>0.48826999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0.75034000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>0.95779000000000003</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B26)</f>
+        <v>0.96431999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>0.96277999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>0.96431999999999995</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>0.95098000000000005</v>
+      </c>
+      <c r="C27">
+        <f>MAX(B27:B29)</f>
+        <v>0.97979000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>0.95459000000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29">
+        <v>0.97979000000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.51185999999999998</v>
+      </c>
+      <c r="C30">
+        <f>MAX(B30:B33)</f>
+        <v>0.82213999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.64922000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>0.67037999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>0.82213999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.74521000000000004</v>
+      </c>
+      <c r="C34">
+        <f>MAX(B34:B36)</f>
+        <v>0.97790999999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>0.96238999999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36">
+        <v>0.97790999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.51105</v>
+      </c>
+      <c r="C37">
+        <f>MAX(B37:B40)</f>
+        <v>0.95711999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.57008999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.95633000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>0.95711999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.95520000000000005</v>
+      </c>
+      <c r="C41">
+        <f>MAX(B41:B44)</f>
+        <v>0.96694999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.94615000000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43">
+        <v>0.94364999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44">
+        <v>0.96694999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814B012A-D937-47C4-8AC9-6A6E5FDF72BE}">
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.74761</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.75158000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.75205</v>
+      </c>
+      <c r="D4">
+        <f>MAX(B2:B5)</f>
+        <v>0.75205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.74997999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.74456999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.74836999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.75007999999999997</v>
+      </c>
+      <c r="D8">
+        <f>MAX(B6:B9)</f>
+        <v>0.75007999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>0.75007999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.71584000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>0.72428000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12">
+        <v>0.74421000000000004</v>
+      </c>
+      <c r="D12">
+        <f>MAX(B10:B13)</f>
+        <v>0.74421000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>0.74414999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14">
+        <v>0.71930000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>0.73812</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>0.74339</v>
+      </c>
+      <c r="D16">
+        <f>MAX(B14:B17)</f>
+        <v>0.74339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>0.74319999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>0.71847000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>0.73836000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>0.74111000000000005</v>
+      </c>
+      <c r="D20">
+        <f>MAX(B18:B21)</f>
+        <v>0.74111000000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>0.74097000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>0.71986000000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>0.71870999999999996</v>
+      </c>
+      <c r="D23">
+        <f>MAX(B22:B24)</f>
+        <v>0.73451999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>0.73451999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>0.71862999999999999</v>
+      </c>
+      <c r="D25">
+        <f>MAX(B25:B27)</f>
+        <v>0.72668999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>0.72275999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>0.72668999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>0.73404000000000003</v>
+      </c>
+      <c r="D28">
+        <f>MAX(B28:B29)</f>
+        <v>0.74175999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29">
+        <v>0.74175999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.65053000000000005</v>
+      </c>
+      <c r="D30">
+        <f>MAX(B30:B31)</f>
+        <v>0.66100999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.66100999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.71103000000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.70535999999999999</v>
+      </c>
+      <c r="D33">
+        <f>MAX(B32:B35)</f>
+        <v>0.72285999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.72285999999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>0.70821999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.73038000000000003</v>
+      </c>
+      <c r="D36">
+        <f>MAX(B36:B38)</f>
+        <v>0.73153999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.73038000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.73153999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>0.71160000000000001</v>
+      </c>
+      <c r="D39">
+        <f>MAX(B39:B42)</f>
+        <v>0.73385</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.72340000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.73385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.72958999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96173FC3-F951-424B-A654-7BA719E64DFA}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.64753000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.65234999999999999</v>
+      </c>
+      <c r="C3">
+        <f>MAX(B2:B4)</f>
+        <v>0.65234999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.63349999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.64115999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.64398999999999995</v>
+      </c>
+      <c r="C6">
+        <f>MAX(B5:B6)</f>
+        <v>0.64398999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0.59609000000000001</v>
+      </c>
+      <c r="C7">
+        <f>MAX(B7:B10)</f>
+        <v>0.61195999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.61195999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.60189999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.46357999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.60346</v>
+      </c>
+      <c r="C11">
+        <f>MAX(B11:B13)</f>
+        <v>0.60728000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.60643000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.60728000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.46994999999999998</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B17)</f>
+        <v>0.58311999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.56738999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.58311999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>0.57865999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.51558999999999999</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B20)</f>
+        <v>0.55315000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.54052999999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.55315000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>0.52388000000000001</v>
+      </c>
+      <c r="C21">
+        <f>MAX(B21:B23)</f>
+        <v>0.52607999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0.52607999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>0.51651000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>0.65505000000000002</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B27)</f>
+        <v>0.66993000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>0.66908000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>0.66993000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>0.64881</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>0.52622000000000002</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B31)</f>
+        <v>0.58672999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>0.57808999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.58672999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.58574000000000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.60218000000000005</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B34)</f>
+        <v>0.60218000000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.40178999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.49008000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>0.56589999999999996</v>
+      </c>
+      <c r="C35">
+        <f>MAX(B35:B38)</f>
+        <v>0.59197999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.59197999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.58248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.58389999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>0.60919999999999996</v>
+      </c>
+      <c r="C39">
+        <f>MAX(B39:B42)</f>
+        <v>0.64966000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.58687999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.64966000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.64753000000000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFC0E0F-6E6F-42A6-8CF4-86ECBE8FE863}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.44827</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B4)</f>
+        <v>0.81762000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.81762000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.63468999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.30153999999999997</v>
+      </c>
+      <c r="C5">
+        <f>MAX(B5:B6)</f>
+        <v>0.72785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.72785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0.43808000000000002</v>
+      </c>
+      <c r="C7">
+        <f>MAX(B7:B10)</f>
+        <v>0.78208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.78208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.72138000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.72423000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.50885000000000002</v>
+      </c>
+      <c r="C11">
+        <f>MAX(B11:B13)</f>
+        <v>0.76607999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.76276999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.76607999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.50876999999999994</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B17)</f>
+        <v>0.78991999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.78991999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.76131000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>0.76400000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.50585000000000002</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B21)</f>
+        <v>0.84753999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.35654000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.84462000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>0.84753999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0.61223000000000005</v>
+      </c>
+      <c r="C22">
+        <f>MAX(B22:B24)</f>
+        <v>0.78900000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>0.78900000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>0.77712000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>0.316</v>
+      </c>
+      <c r="C25">
+        <f>MAX(B25:B27)</f>
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>0.27792</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>0.26430999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>0.69191999999999998</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B31)</f>
+        <v>0.69191999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>0.62185000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.65207999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.66554000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.41685</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B35)</f>
+        <v>0.71584999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.71584999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.67945999999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>0.69762000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.48437999999999998</v>
+      </c>
+      <c r="C36">
+        <f>MAX(B36:B38)</f>
+        <v>0.79884999999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.79884999999999995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.79408000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>0.50680999999999998</v>
+      </c>
+      <c r="C39">
+        <f>MAX(B39:B42)</f>
+        <v>0.63968999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.46515000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.38338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.63968999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF3F352-3EF6-4C40-860C-2F33291BDFA8}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.99577000000000004</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B3)</f>
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>0.99155000000000004</v>
+      </c>
+      <c r="C4">
+        <f>MAX(B4:B6)</f>
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.99436999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0.99248999999999998</v>
+      </c>
+      <c r="C7">
+        <f>MAX(B7:B9)</f>
+        <v>0.99670999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.99531000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.99670999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>0.99295999999999995</v>
+      </c>
+      <c r="C10">
+        <f>MAX(B10:B11)</f>
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>0.97840000000000005</v>
+      </c>
+      <c r="C12">
+        <f>MAX(B12:B14)</f>
+        <v>0.98028000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13">
+        <v>0.97887000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.98028000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>0.95728000000000002</v>
+      </c>
+      <c r="C15">
+        <f>MAX(B15:B17)</f>
+        <v>0.96526000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.96338000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.96526000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>0.95962000000000003</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B20)</f>
+        <v>0.96736999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>0.96103000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.96736999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>0.99343000000000004</v>
+      </c>
+      <c r="C21">
+        <f>MAX(B21:B23)</f>
+        <v>0.99483999999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.99436999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>0.99483999999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>0.64788999999999997</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B27)</f>
+        <v>0.64788999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>0.6169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0.62770000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>0.55586999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>0.99060999999999999</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B30)</f>
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>0.99624000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <v>0.99717999999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="C31">
+        <f>B31</f>
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32">
+        <v>0.99436999999999998</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B33)</f>
+        <v>0.99436999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>0.99202000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A4D3B8-EA7D-4BBD-950A-F6390B43B165}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.55615000000000003</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B5)</f>
+        <v>0.57347000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.56925999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.57174000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.57347000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.55745</v>
+      </c>
+      <c r="C6">
+        <f>MAX(B6:B8)</f>
+        <v>0.56618000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.56489999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.56618000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.47383999999999998</v>
+      </c>
+      <c r="C9">
+        <f>MAX(B9:B11)</f>
+        <v>0.47383999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.46977000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>0.44077</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.50119000000000002</v>
+      </c>
+      <c r="C12">
+        <f>MAX(B12:B13)</f>
+        <v>0.50119000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.41348000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.48381000000000002</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B15)</f>
+        <v>0.49658000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.49658000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.46695999999999999</v>
+      </c>
+      <c r="C16">
+        <f>MAX(B16:B19)</f>
+        <v>0.47960000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.47960000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.47815000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.42636000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.51495000000000002</v>
+      </c>
+      <c r="C20">
+        <f>MAX(B20:B23)</f>
+        <v>0.51910000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>0.51861999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0.51910000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>0.51822000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>0.43720999999999999</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B25)</f>
+        <v>0.43720999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>0.42781999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0.45831</v>
+      </c>
+      <c r="C26">
+        <f>MAX(B26:B29)</f>
+        <v>0.47666999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>0.41425000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>0.47589999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>0.47666999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <v>0.48171000000000003</v>
+      </c>
+      <c r="C30">
+        <f>MAX(B30:B33)</f>
+        <v>0.53641000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31">
+        <v>0.48127999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.53117999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.53641000000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>0.47381000000000001</v>
+      </c>
+      <c r="C34">
+        <f>MAX(B34:B36)</f>
+        <v>0.47381000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>0.47099000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.44855</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37">
+        <v>0.48259000000000002</v>
+      </c>
+      <c r="C37">
+        <f>MAX(B37:B38)</f>
+        <v>0.49945000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>0.49945000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8B5A3-CE5B-4A8C-9C85-AF312DF32E51}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.54093000000000002</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B3)</f>
+        <v>0.54093000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.50585000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>0.51951999999999998</v>
+      </c>
+      <c r="C4">
+        <f>MAX(B4:B7)</f>
+        <v>0.53190999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.53190999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.52966000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.52924000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.52049999999999996</v>
+      </c>
+      <c r="C8">
+        <f>MAX(B8:B10)</f>
+        <v>0.52542999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.52542999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.52431000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.50183</v>
+      </c>
+      <c r="C11">
+        <f>MAX(B11:B13)</f>
+        <v>0.50183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.46189000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.49682999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.50183</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B16)</f>
+        <v>0.50183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.47619</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.49084</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.50007000000000001</v>
+      </c>
+      <c r="C17">
+        <f>MAX(B17:B18)</f>
+        <v>0.50344999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.50344999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>0.50726000000000004</v>
+      </c>
+      <c r="C19">
+        <f>MAX(B19:B20)</f>
+        <v>0.50726000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.48048000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>0.52669999999999995</v>
+      </c>
+      <c r="C21">
+        <f>MAX(B21:B23)</f>
+        <v>0.53417000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.53036000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>0.53417000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>0.51853000000000005</v>
+      </c>
+      <c r="C24">
+        <f>MAX(B24:B26)</f>
+        <v>0.51853000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>0.51726000000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0.49556</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>0.53205999999999998</v>
+      </c>
+      <c r="C27">
+        <f>MAX(B27:B29)</f>
+        <v>0.58291999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>0.56559000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>0.58291999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>0.48837999999999998</v>
+      </c>
+      <c r="C30">
+        <f>MAX(B30:B32)</f>
+        <v>0.49569999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>0.47089999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>0.49569999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>0.54615000000000002</v>
+      </c>
+      <c r="C33">
+        <f>MAX(B33:B35)</f>
+        <v>0.55686000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>0.55318999999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>0.55686000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B796E0-256A-4A27-9A69-9963FBE3B123}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.68010999999999999</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B5)</f>
+        <v>0.68383000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.68383000000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.67630999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.68213999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.66056000000000004</v>
+      </c>
+      <c r="C6">
+        <f>MAX(B6:B8)</f>
+        <v>0.66883000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>0.66861000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.66883000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.62133000000000005</v>
+      </c>
+      <c r="C9">
+        <f>MAX(B9:B10)</f>
+        <v>0.65583000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.65583000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.54978000000000005</v>
+      </c>
+      <c r="C11">
+        <f>MAX(B11:B13)</f>
+        <v>0.56933</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>0.56760999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13">
+        <v>0.56933</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.48764000000000002</v>
+      </c>
+      <c r="C14">
+        <f>MAX(B14:B17)</f>
+        <v>0.56138999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>0.54483000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>0.54805999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>0.56138999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.48566999999999999</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B20)</f>
+        <v>0.56906000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>0.56521999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>0.56906000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>0.58743999999999996</v>
+      </c>
+      <c r="C21">
+        <f>MAX(B21:B24)</f>
+        <v>0.60592000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0.60592000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>0.60472000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>0.59699999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>0.74978</v>
+      </c>
+      <c r="C25">
+        <f>MAX(B25:B27)</f>
+        <v>0.75566999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>0.75217000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>0.75566999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>0.52010999999999996</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B31)</f>
+        <v>0.55693999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>0.54117000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>0.55393999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>0.55693999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>0.66439000000000004</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B35)</f>
+        <v>0.72055999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>0.71494000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34">
+        <v>0.72055999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>0.70011000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>0.54471999999999998</v>
+      </c>
+      <c r="C36">
+        <f>MAX(B36:B39)</f>
+        <v>0.55967</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0.55967</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>0.54881000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.55528</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.70977999999999997</v>
+      </c>
+      <c r="C40">
+        <f>MAX(B40:B43)</f>
+        <v>0.71682999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>0.71150000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>0.71011000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43">
+        <v>0.71682999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F9DFA3-0E78-460F-9480-3FC988D2C4F5}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>0.84877999999999998</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B4)</f>
+        <v>0.87480000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.86938000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.87480000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.88319999999999999</v>
+      </c>
+      <c r="C5">
+        <f>MAX(B5:B6)</f>
+        <v>0.88319999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.86775000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0.67642000000000002</v>
+      </c>
+      <c r="C7">
+        <f>MAX(B7:B9)</f>
+        <v>0.86667000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0.58808000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.86667000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>0.64173000000000002</v>
+      </c>
+      <c r="C10">
+        <f>MAX(B10:B11)</f>
+        <v>0.86504000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0.86504000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>0.67317000000000005</v>
+      </c>
+      <c r="C12">
+        <f>MAX(B12:B14)</f>
+        <v>0.83957000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13">
+        <v>0.61761999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>0.83957000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>0.58699000000000001</v>
+      </c>
+      <c r="C15">
+        <f>MAX(B15:B17)</f>
+        <v>0.77886</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0.73333000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.77886</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>0.5393</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B21)</f>
+        <v>0.72926999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>0.55501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.72926999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>0.71220000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>0.78861999999999999</v>
+      </c>
+      <c r="C22">
+        <f>MAX(B22:B24)</f>
+        <v>0.85799000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>0.84714999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>0.85799000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>0.50678000000000001</v>
+      </c>
+      <c r="C25">
+        <f>MAX(B25:B27)</f>
+        <v>0.74200999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0.71762000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>0.74200999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>0.65256999999999998</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B31)</f>
+        <v>0.90351999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>0.60487999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <v>0.62385000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31">
+        <v>0.90351999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>0.69621</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B34)</f>
+        <v>0.80379</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>0.74958999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>0.80379</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>0.61680000000000001</v>
+      </c>
+      <c r="C35">
+        <f>MAX(B35:B37)</f>
+        <v>0.89539000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>0.87858999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37">
+        <v>0.89539000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029DDA5-1006-487A-BF27-0EBDCC949AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450FCC62-08DB-436E-9DF5-C0C166FAD645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="41">
   <si>
     <t>Arrhy</t>
   </si>
@@ -189,7 +189,10 @@
     <t>COF</t>
   </si>
   <si>
-    <t>Average/Count</t>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Count that beats</t>
   </si>
 </sst>
 </file>
@@ -248,13 +251,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1089,14 +1093,6 @@
         <f>AVERAGE(H2:H12)</f>
         <v>0.93570909090909093</v>
       </c>
-      <c r="I13" s="5">
-        <f>COUNTIF(I2:I12,"&gt;0")</f>
-        <v>4</v>
-      </c>
-      <c r="J13" s="5">
-        <f>COUNTIF(J2:J12,"&gt;0")</f>
-        <v>8</v>
-      </c>
       <c r="L13" s="1">
         <f>AVERAGE(L2:L12)</f>
         <v>0.78765090909090918</v>
@@ -1149,6 +1145,22 @@
         <f>AVERAGE(Arrhythmia!D39,Parkinson!C39,Shuttle!C39,WBC!C32,SpamBase!C37,WPBC!C33,HeartDisease!C40,Glass!C35,Hep!C39,Pima!C32,PenDigits!C41)</f>
         <v>0.74376999999999993</v>
       </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="5">
+        <f>COUNTIF(I2:I12,"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="J14" s="5">
+        <f>COUNTIF(J2:J12,"&gt;0")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="J15" s="6"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450FCC62-08DB-436E-9DF5-C0C166FAD645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5B9A97-411B-4AA5-B419-D33A02599AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
-    <sheet name="Arrhythmia" sheetId="2" r:id="rId2"/>
-    <sheet name="Parkinson" sheetId="3" r:id="rId3"/>
-    <sheet name="Shuttle" sheetId="4" r:id="rId4"/>
-    <sheet name="WBC" sheetId="5" r:id="rId5"/>
-    <sheet name="SpamBase" sheetId="6" r:id="rId6"/>
-    <sheet name="WPBC" sheetId="7" r:id="rId7"/>
-    <sheet name="HeartDisease" sheetId="8" r:id="rId8"/>
-    <sheet name="Glass" sheetId="9" r:id="rId9"/>
-    <sheet name="Hep" sheetId="10" r:id="rId10"/>
-    <sheet name="Pima" sheetId="11" r:id="rId11"/>
-    <sheet name="PenDigits" sheetId="12" r:id="rId12"/>
+    <sheet name="Latex" sheetId="14" r:id="rId2"/>
+    <sheet name="Arrhythmia" sheetId="2" r:id="rId3"/>
+    <sheet name="Parkinson" sheetId="3" r:id="rId4"/>
+    <sheet name="Shuttle" sheetId="4" r:id="rId5"/>
+    <sheet name="WBC" sheetId="5" r:id="rId6"/>
+    <sheet name="SpamBase" sheetId="6" r:id="rId7"/>
+    <sheet name="WPBC" sheetId="7" r:id="rId8"/>
+    <sheet name="HeartDisease" sheetId="8" r:id="rId9"/>
+    <sheet name="Glass" sheetId="9" r:id="rId10"/>
+    <sheet name="Hep" sheetId="10" r:id="rId11"/>
+    <sheet name="Pima" sheetId="11" r:id="rId12"/>
+    <sheet name="PenDigits" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="37">
   <si>
     <t>Arrhy</t>
   </si>
@@ -85,9 +86,6 @@
     <t>Dataset</t>
   </si>
   <si>
-    <t>Skewed Normal</t>
-  </si>
-  <si>
     <t>Gamma</t>
   </si>
   <si>
@@ -103,28 +101,10 @@
     <t>LDF</t>
   </si>
   <si>
-    <t>SN R^2 Q-Q</t>
-  </si>
-  <si>
     <t>Gamma R^2 Q-Q</t>
   </si>
   <si>
-    <t>Paper Best</t>
-  </si>
-  <si>
-    <t>Best-Algo</t>
-  </si>
-  <si>
-    <t>Difference Skewed Normal</t>
-  </si>
-  <si>
     <t>Gamma uses manhattan distance</t>
-  </si>
-  <si>
-    <t>Difference Best Algo</t>
-  </si>
-  <si>
-    <t>Difference KNN</t>
   </si>
   <si>
     <r>
@@ -151,9 +131,6 @@
       </rPr>
       <t xml:space="preserve"> Q-Q</t>
     </r>
-  </si>
-  <si>
-    <t>Paper-KNN</t>
   </si>
   <si>
     <t>Gamma AUC</t>
@@ -194,16 +171,49 @@
   <si>
     <t>Count that beats</t>
   </si>
+  <si>
+    <r>
+      <t>Gamma Q-Q Plot R</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>State of Art</t>
+  </si>
+  <si>
+    <t>Proposed</t>
+  </si>
+  <si>
+    <t>Arrhythmia</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -238,7 +248,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -246,25 +256,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -540,26 +611,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="3" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="10" width="25.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -567,73 +632,49 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" t="s">
-        <v>27</v>
-      </c>
       <c r="N1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="O1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -643,41 +684,47 @@
       <c r="C2">
         <v>0.93830000000000002</v>
       </c>
-      <c r="D2">
-        <v>0.76108148973420298</v>
-      </c>
-      <c r="E2">
-        <v>0.98860000000000003</v>
-      </c>
-      <c r="F2" s="2">
-        <f>B2-L2</f>
-        <v>1.0026500079578948E-2</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.76108148973420298</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="D2" s="2">
         <v>0.97450000000000003</v>
       </c>
-      <c r="I2" s="3">
-        <f>G2-L2</f>
-        <v>9.0814897342029743E-3</v>
-      </c>
-      <c r="J2" s="3">
-        <f t="shared" ref="J2:J12" si="0">G2-M2</f>
-        <v>9.0814897342029743E-3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="E2" s="1">
         <v>0.752</v>
       </c>
-      <c r="M2" s="1">
-        <v>0.752</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>0.75007999999999997</v>
+      </c>
+      <c r="G2">
+        <v>0.74421000000000004</v>
+      </c>
+      <c r="H2">
+        <v>0.74339</v>
+      </c>
+      <c r="I2">
+        <v>0.74111000000000005</v>
+      </c>
+      <c r="J2">
+        <v>0.73451999999999995</v>
+      </c>
+      <c r="K2">
+        <v>0.72668999999999995</v>
+      </c>
+      <c r="L2">
+        <v>0.74175999999999997</v>
+      </c>
+      <c r="M2">
+        <v>0.66100999999999999</v>
+      </c>
+      <c r="N2">
+        <v>0.72285999999999995</v>
+      </c>
+      <c r="O2">
+        <v>0.73153999999999997</v>
+      </c>
+      <c r="P2">
+        <v>0.73385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -687,41 +734,47 @@
       <c r="C3">
         <v>0.81930000000000003</v>
       </c>
-      <c r="D3">
-        <v>0.73816609977324199</v>
+      <c r="D3" s="2">
+        <v>0.85409999999999997</v>
       </c>
       <c r="E3">
-        <v>0.88660000000000005</v>
-      </c>
-      <c r="F3" s="2">
-        <f t="shared" ref="F3:F12" si="1">B3-L3</f>
-        <v>6.9654195011336961E-2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.73816609977324199</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.85409999999999997</v>
-      </c>
-      <c r="I3" s="3">
-        <f t="shared" ref="I3:I12" si="2">G3-L3</f>
-        <v>6.816609977324195E-2</v>
-      </c>
-      <c r="J3" s="3">
-        <f t="shared" si="0"/>
-        <v>8.5816099773242005E-2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0.67</v>
+        <v>0.65234999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.64398999999999995</v>
+      </c>
+      <c r="G3">
+        <v>0.61195999999999995</v>
+      </c>
+      <c r="H3">
+        <v>0.60728000000000004</v>
+      </c>
+      <c r="I3">
+        <v>0.58311999999999997</v>
+      </c>
+      <c r="J3">
+        <v>0.55315000000000003</v>
+      </c>
+      <c r="K3">
+        <v>0.52607999999999999</v>
+      </c>
+      <c r="L3">
+        <v>0.66993000000000003</v>
       </c>
       <c r="M3">
-        <v>0.65234999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.58672999999999997</v>
+      </c>
+      <c r="N3">
+        <v>0.60218000000000005</v>
+      </c>
+      <c r="O3">
+        <v>0.59197999999999995</v>
+      </c>
+      <c r="P3">
+        <v>0.64966000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -731,38 +784,47 @@
       <c r="C4">
         <v>0.65539999999999998</v>
       </c>
-      <c r="D4">
-        <v>0.82015384615384601</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" si="1"/>
-        <v>-1.9246153846159686E-3</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.82015384615384601</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="D4" s="2">
         <v>0.72499999999999998</v>
       </c>
-      <c r="I4" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.7386153846153949E-2</v>
-      </c>
-      <c r="J4" s="3">
-        <f t="shared" si="0"/>
-        <v>2.5338461538459978E-3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="E4">
+        <v>0.81762000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.72785</v>
+      </c>
+      <c r="G4">
+        <v>0.78208</v>
+      </c>
+      <c r="H4">
+        <v>0.76607999999999998</v>
+      </c>
+      <c r="I4">
+        <v>0.78991999999999996</v>
+      </c>
+      <c r="J4">
         <v>0.84753999999999996</v>
       </c>
+      <c r="K4">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="L4">
+        <v>0.316</v>
+      </c>
       <c r="M4">
-        <v>0.81762000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.69191999999999998</v>
+      </c>
+      <c r="N4">
+        <v>0.71584999999999999</v>
+      </c>
+      <c r="O4">
+        <v>0.79884999999999995</v>
+      </c>
+      <c r="P4">
+        <v>0.63968999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -772,38 +834,47 @@
       <c r="C5">
         <v>0.72529999999999994</v>
       </c>
-      <c r="D5">
-        <v>0.99859154929577398</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="1"/>
-        <v>-4.6917370892020083E-3</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.99859154929577398</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="D5" s="2">
         <v>0.98670000000000002</v>
       </c>
-      <c r="I5" s="3">
-        <f t="shared" si="2"/>
-        <v>1.4115492957740283E-3</v>
-      </c>
-      <c r="J5" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4115492957740283E-3</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="E5">
         <v>0.99717999999999996</v>
       </c>
+      <c r="F5">
+        <v>0.99717999999999996</v>
+      </c>
+      <c r="G5">
+        <v>0.99670999999999998</v>
+      </c>
+      <c r="H5">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0.98028000000000004</v>
+      </c>
+      <c r="J5">
+        <v>0.96526000000000001</v>
+      </c>
+      <c r="K5">
+        <v>0.96736999999999995</v>
+      </c>
+      <c r="L5">
+        <v>0.99483999999999995</v>
+      </c>
       <c r="M5">
+        <v>0.64788999999999997</v>
+      </c>
+      <c r="N5">
         <v>0.99717999999999996</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="O5">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="P5">
+        <v>0.99436999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -813,35 +884,47 @@
       <c r="C6">
         <v>0.88929999999999998</v>
       </c>
-      <c r="F6" s="2">
-        <f t="shared" si="1"/>
-        <v>7.7279367654042974E-2</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.65000947105344398</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="D6" s="2">
         <v>0.92220000000000002</v>
       </c>
-      <c r="I6" s="3">
-        <f t="shared" si="2"/>
-        <v>7.6539471053443942E-2</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" si="0"/>
-        <v>7.6539471053443942E-2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="E6">
         <v>0.57347000000000004</v>
       </c>
+      <c r="F6">
+        <v>0.56618000000000002</v>
+      </c>
+      <c r="G6">
+        <v>0.47383999999999998</v>
+      </c>
+      <c r="H6">
+        <v>0.50119000000000002</v>
+      </c>
+      <c r="I6">
+        <v>0.49658000000000002</v>
+      </c>
+      <c r="J6">
+        <v>0.47960000000000003</v>
+      </c>
+      <c r="K6">
+        <v>0.51910000000000001</v>
+      </c>
+      <c r="L6">
+        <v>0.43720999999999999</v>
+      </c>
       <c r="M6">
-        <v>0.57347000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.47666999999999998</v>
+      </c>
+      <c r="N6">
+        <v>0.53641000000000005</v>
+      </c>
+      <c r="O6">
+        <v>0.47381000000000001</v>
+      </c>
+      <c r="P6">
+        <v>0.49945000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -851,35 +934,47 @@
       <c r="C7">
         <v>0.95530000000000004</v>
       </c>
-      <c r="F7" s="2">
-        <f t="shared" si="1"/>
-        <v>-5.3541389319430976E-2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.53156263209806898</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="D7" s="2">
         <v>0.98599999999999999</v>
       </c>
-      <c r="I7" s="3">
-        <f t="shared" si="2"/>
-        <v>-5.1357367901931017E-2</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="0"/>
-        <v>-9.3373679019310707E-3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="E7" s="3">
+        <v>0.54090000000000005</v>
+      </c>
+      <c r="F7">
+        <v>0.53190999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0.52542999999999995</v>
+      </c>
+      <c r="H7">
+        <v>0.50183</v>
+      </c>
+      <c r="I7">
+        <v>0.50183</v>
+      </c>
+      <c r="J7">
+        <v>0.50344999999999995</v>
+      </c>
+      <c r="K7">
+        <v>0.50726000000000004</v>
+      </c>
+      <c r="L7">
+        <v>0.53417000000000003</v>
+      </c>
+      <c r="M7">
+        <v>0.51853000000000005</v>
+      </c>
+      <c r="N7">
         <v>0.58291999999999999</v>
       </c>
-      <c r="M7" s="4">
-        <v>0.54090000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="O7">
+        <v>0.49569999999999997</v>
+      </c>
+      <c r="P7">
+        <v>0.55686000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -889,35 +984,47 @@
       <c r="C8">
         <v>0.99519999999999997</v>
       </c>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
-        <v>-5.6781111111110949E-2</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.70016666666666605</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="D8" s="2">
         <v>0.99390000000000001</v>
       </c>
-      <c r="I8" s="3">
-        <f t="shared" si="2"/>
-        <v>-5.5503333333333904E-2</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="0"/>
-        <v>1.6336666666666E-2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="E8">
+        <v>0.68383000000000005</v>
+      </c>
+      <c r="F8">
+        <v>0.66883000000000004</v>
+      </c>
+      <c r="G8">
+        <v>0.65583000000000002</v>
+      </c>
+      <c r="H8">
+        <v>0.56933</v>
+      </c>
+      <c r="I8">
+        <v>0.56138999999999994</v>
+      </c>
+      <c r="J8">
+        <v>0.56906000000000001</v>
+      </c>
+      <c r="K8">
+        <v>0.60592000000000001</v>
+      </c>
+      <c r="L8">
         <v>0.75566999999999995</v>
       </c>
       <c r="M8">
-        <v>0.68383000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.55693999999999999</v>
+      </c>
+      <c r="N8">
+        <v>0.72055999999999998</v>
+      </c>
+      <c r="O8">
+        <v>0.55967</v>
+      </c>
+      <c r="P8">
+        <v>0.71682999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -927,35 +1034,47 @@
       <c r="C9">
         <v>0.8196</v>
       </c>
-      <c r="F9" s="2">
-        <f t="shared" si="1"/>
-        <v>-2.6284227642277003E-2</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.88048780487804801</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="D9" s="2">
         <v>0.93869999999999998</v>
       </c>
-      <c r="I9" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.3032195121951982E-2</v>
-      </c>
-      <c r="J9" s="3">
-        <f t="shared" si="0"/>
-        <v>5.6878048780479862E-3</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="E9">
+        <v>0.87480000000000002</v>
+      </c>
+      <c r="F9">
+        <v>0.88319999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0.86667000000000005</v>
+      </c>
+      <c r="H9">
+        <v>0.86504000000000003</v>
+      </c>
+      <c r="I9">
+        <v>0.83957000000000004</v>
+      </c>
+      <c r="J9">
+        <v>0.77886</v>
+      </c>
+      <c r="K9">
+        <v>0.72926999999999997</v>
+      </c>
+      <c r="L9">
+        <v>0.85799000000000003</v>
+      </c>
+      <c r="M9">
+        <v>0.74200999999999995</v>
+      </c>
+      <c r="N9">
         <v>0.90351999999999999</v>
       </c>
-      <c r="M9">
-        <v>0.87480000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="O9">
+        <v>0.80379</v>
+      </c>
+      <c r="P9">
+        <v>0.89539000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -965,35 +1084,47 @@
       <c r="C10">
         <v>0.96850000000000003</v>
       </c>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>-4.3625752009184948E-2</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.78473019517795595</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="D10" s="2">
         <v>0.93610000000000004</v>
       </c>
-      <c r="I10" s="3">
-        <f t="shared" si="2"/>
-        <v>-4.4199804822043998E-2</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="0"/>
-        <v>-1.149804822044076E-3</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="E10">
+        <v>0.78588000000000002</v>
+      </c>
+      <c r="F10">
+        <v>0.74856</v>
+      </c>
+      <c r="G10">
+        <v>0.80367</v>
+      </c>
+      <c r="H10">
+        <v>0.73823000000000005</v>
+      </c>
+      <c r="I10">
+        <v>0.72331000000000001</v>
+      </c>
+      <c r="J10">
+        <v>0.73823000000000005</v>
+      </c>
+      <c r="K10">
+        <v>0.74970999999999999</v>
+      </c>
+      <c r="L10">
+        <v>0.70952999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.71182999999999996</v>
+      </c>
+      <c r="N10">
         <v>0.82892999999999994</v>
       </c>
-      <c r="M10">
-        <v>0.78588000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="O10">
+        <v>0.60275999999999996</v>
+      </c>
+      <c r="P10">
+        <v>0.82721</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1003,35 +1134,47 @@
       <c r="C11">
         <v>0.99199999999999999</v>
       </c>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>-2.554134328358304E-2</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.73591417910447698</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="D11" s="2">
         <v>0.997</v>
       </c>
-      <c r="I11" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.4895820895523002E-2</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="0"/>
-        <v>3.6741791044769823E-3</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="E11">
+        <v>0.73224</v>
+      </c>
+      <c r="F11">
+        <v>0.72943999999999998</v>
+      </c>
+      <c r="G11">
+        <v>0.68955</v>
+      </c>
+      <c r="H11">
+        <v>0.62131000000000003</v>
+      </c>
+      <c r="I11">
+        <v>0.60921999999999998</v>
+      </c>
+      <c r="J11">
+        <v>0.57003999999999999</v>
+      </c>
+      <c r="K11">
+        <v>0.63636999999999999</v>
+      </c>
+      <c r="L11">
         <v>0.76080999999999999</v>
       </c>
       <c r="M11">
-        <v>0.73224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.55620999999999998</v>
+      </c>
+      <c r="N11">
+        <v>0.72887999999999997</v>
+      </c>
+      <c r="O11">
+        <v>0.61728000000000005</v>
+      </c>
+      <c r="P11">
+        <v>0.70121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1041,37 +1184,49 @@
       <c r="C12">
         <v>0.97070000000000001</v>
       </c>
-      <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>-9.7250974817230107E-3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.98260560519902496</v>
-      </c>
-      <c r="H12" s="2">
+      <c r="D12" s="2">
         <v>0.97860000000000003</v>
       </c>
-      <c r="I12" s="3">
-        <f t="shared" si="2"/>
-        <v>-9.5143948009750456E-3</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="0"/>
-        <v>-9.5143948009750456E-3</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="E12" s="1">
         <v>0.99212</v>
       </c>
-      <c r="M12" s="1">
-        <v>0.99212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="G12">
+        <v>0.96580999999999995</v>
+      </c>
+      <c r="H12">
+        <v>0.96679999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0.96231</v>
+      </c>
+      <c r="J12">
+        <v>0.75034000000000001</v>
+      </c>
+      <c r="K12">
+        <v>0.96431999999999995</v>
+      </c>
+      <c r="L12">
+        <v>0.97979000000000005</v>
+      </c>
+      <c r="M12">
+        <v>0.82213999999999998</v>
+      </c>
+      <c r="N12">
+        <v>0.97790999999999995</v>
+      </c>
+      <c r="O12">
+        <v>0.95711999999999997</v>
+      </c>
+      <c r="P12">
+        <v>0.96694999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <f>AVERAGE(B2:B12)</f>
@@ -1081,90 +1236,67 @@
         <f>AVERAGE(C2:C12)</f>
         <v>0.88444545454545453</v>
       </c>
-      <c r="F13" s="2">
-        <f>B13-L13</f>
-        <v>-5.9232009614700321E-3</v>
-      </c>
-      <c r="G13" s="3">
-        <f>AVERAGE(G2:G12)</f>
-        <v>0.7803154126486137</v>
-      </c>
-      <c r="H13" s="2">
-        <f>AVERAGE(H2:H12)</f>
+      <c r="D13" s="2">
+        <f>AVERAGE(D2:D12)</f>
         <v>0.93570909090909093</v>
       </c>
-      <c r="L13" s="1">
-        <f>AVERAGE(L2:L12)</f>
-        <v>0.78765090909090918</v>
-      </c>
-      <c r="M13" s="2">
-        <f>AVERAGE(M2:M12)</f>
+      <c r="E13" s="2">
+        <f>AVERAGE(E2:E12)</f>
         <v>0.76385363636363646</v>
       </c>
+      <c r="F13">
+        <f>AVERAGE(F2:F12)</f>
+        <v>0.74898363636363641</v>
+      </c>
+      <c r="G13">
+        <f t="shared" ref="G13:P13" si="0">AVERAGE(G2:G12)</f>
+        <v>0.73779636363636358</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0.71585272727272731</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>0.7080581818181817</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>0.68091363636363633</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>0.70191727272727278</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>0.70524545454545462</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>0.63380727272727266</v>
+      </c>
       <c r="N13">
-        <f>AVERAGE(Arrhythmia!D8,Parkinson!C6,Shuttle!C5,WBC!C4,SpamBase!C6,WPBC!C4,HeartDisease!C6,Glass!C5,Hep!C5,Pima!C6,PenDigits!C5)</f>
-        <v>0.74898363636363641</v>
+        <f t="shared" si="0"/>
+        <v>0.75610909090909084</v>
       </c>
       <c r="O13">
-        <f>AVERAGE(Arrhythmia!D12,Parkinson!C7,Shuttle!C7,WBC!C7,SpamBase!C9,WPBC!C8,HeartDisease!C9,Glass!C7,Hep!C8,Pima!C10,PenDigits!C9)</f>
-        <v>0.73779636363636358</v>
+        <f t="shared" si="0"/>
+        <v>0.69330909090909087</v>
       </c>
       <c r="P13">
-        <f>AVERAGE(Arrhythmia!D16,Parkinson!C11,Shuttle!C11,WBC!C10,SpamBase!C12,WPBC!C11,HeartDisease!C11,Glass!C10,Hep!C11,Pima!C12,PenDigits!C13)</f>
-        <v>0.71585272727272731</v>
-      </c>
-      <c r="Q13">
-        <f>AVERAGE(Arrhythmia!D20,Parkinson!C14,Shuttle!C14,WBC!C12,SpamBase!C14,WPBC!C14,HeartDisease!C14,Glass!C12,Hep!C15,Pima!C14,PenDigits!C16)</f>
-        <v>0.7080581818181817</v>
-      </c>
-      <c r="R13">
-        <f>AVERAGE(Arrhythmia!D23,Parkinson!C18,Shuttle!C18,WBC!C15,SpamBase!C16,WPBC!C17,HeartDisease!C18,Glass!C15,Hep!C19,Pima!C16,PenDigits!C20)</f>
-        <v>0.68091363636363633</v>
-      </c>
-      <c r="S13">
-        <f>AVERAGE(Arrhythmia!D25,Parkinson!C21,Shuttle!C22,WBC!C18,SpamBase!C20,WPBC!C19,HeartDisease!C21,Glass!C18,Hep!C22,Pima!C20,PenDigits!C24)</f>
-        <v>0.70191727272727278</v>
-      </c>
-      <c r="T13">
-        <f>AVERAGE(Arrhythmia!D28,Parkinson!C24,Shuttle!C25,WBC!C21,SpamBase!C24,WPBC!C21,HeartDisease!C25,Glass!C22,Hep!C26,Pima!C21,PenDigits!C27)</f>
-        <v>0.70524545454545462</v>
-      </c>
-      <c r="U13">
-        <f>AVERAGE(Arrhythmia!D30,Parkinson!C28,Shuttle!C28,WBC!C24,SpamBase!C26,WPBC!C24,HeartDisease!C28,Glass!C25,Hep!C29,Pima!C24,PenDigits!C30)</f>
-        <v>0.63380727272727266</v>
-      </c>
-      <c r="V13">
-        <f>AVERAGE(Arrhythmia!D33,Parkinson!C32,Shuttle!C32,WBC!C28,SpamBase!C30,WPBC!C27,HeartDisease!C32,Glass!C28,Hep!C32,Pima!C26,PenDigits!C34)</f>
-        <v>0.75610909090909084</v>
-      </c>
-      <c r="W13">
-        <f>AVERAGE(Arrhythmia!D36,Parkinson!C35,Shuttle!C36,WBC!C31,SpamBase!C34,WPBC!C30,HeartDisease!C36,Glass!C32,Hep!C36,Pima!C29,PenDigits!C37)</f>
-        <v>0.69330909090909087</v>
-      </c>
-      <c r="X13">
-        <f>AVERAGE(Arrhythmia!D39,Parkinson!C39,Shuttle!C39,WBC!C32,SpamBase!C37,WPBC!C33,HeartDisease!C40,Glass!C35,Hep!C39,Pima!C32,PenDigits!C41)</f>
+        <f t="shared" si="0"/>
         <v>0.74376999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="5">
-        <f>COUNTIF(I2:I12,"&gt;0")</f>
-        <v>4</v>
-      </c>
-      <c r="J14" s="5">
-        <f>COUNTIF(J2:J12,"&gt;0")</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="J15" s="6"/>
+        <v>32</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1174,21 +1306,375 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F9DFA3-0E78-460F-9480-3FC988D2C4F5}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>0.84877999999999998</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2:B4)</f>
+        <v>0.87480000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>0.86938000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>0.87480000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>0.88319999999999999</v>
+      </c>
+      <c r="C5">
+        <f>MAX(B5:B6)</f>
+        <v>0.88319999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>0.86775000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.67642000000000002</v>
+      </c>
+      <c r="C7">
+        <f>MAX(B7:B9)</f>
+        <v>0.86667000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>0.58808000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>0.86667000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>0.64173000000000002</v>
+      </c>
+      <c r="C10">
+        <f>MAX(B10:B11)</f>
+        <v>0.86504000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>0.86504000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>0.67317000000000005</v>
+      </c>
+      <c r="C12">
+        <f>MAX(B12:B14)</f>
+        <v>0.83957000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>0.61761999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>0.83957000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0.58699000000000001</v>
+      </c>
+      <c r="C15">
+        <f>MAX(B15:B17)</f>
+        <v>0.77886</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.73333000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.77886</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>0.5393</v>
+      </c>
+      <c r="C18">
+        <f>MAX(B18:B21)</f>
+        <v>0.72926999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>0.55501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>0.72926999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <v>0.71220000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22">
+        <v>0.78861999999999999</v>
+      </c>
+      <c r="C22">
+        <f>MAX(B22:B24)</f>
+        <v>0.85799000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23">
+        <v>0.84714999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24">
+        <v>0.85799000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
+        <v>0.50678000000000001</v>
+      </c>
+      <c r="C25">
+        <f>MAX(B25:B27)</f>
+        <v>0.74200999999999995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>0.71762000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>0.74200999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <v>0.65256999999999998</v>
+      </c>
+      <c r="C28">
+        <f>MAX(B28:B31)</f>
+        <v>0.90351999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29">
+        <v>0.60487999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30">
+        <v>0.62385000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31">
+        <v>0.90351999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>0.69621</v>
+      </c>
+      <c r="C32">
+        <f>MAX(B32:B34)</f>
+        <v>0.80379</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33">
+        <v>0.74958999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34">
+        <v>0.80379</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35">
+        <v>0.61680000000000001</v>
+      </c>
+      <c r="C35">
+        <f>MAX(B35:B37)</f>
+        <v>0.89539000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36">
+        <v>0.87858999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>0.89539000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEBCE60-A305-4996-8394-EDFED30DAA67}">
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.78588000000000002</v>
@@ -1200,7 +1686,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.77842</v>
@@ -1208,7 +1694,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.77612000000000003</v>
@@ -1216,7 +1702,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.69116</v>
@@ -1228,7 +1714,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.74856</v>
@@ -1236,7 +1722,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.74168000000000001</v>
@@ -1244,7 +1730,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.76693</v>
@@ -1256,7 +1742,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.80023</v>
@@ -1264,7 +1750,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.80367</v>
@@ -1272,7 +1758,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.72789999999999999</v>
@@ -1284,7 +1770,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.73363999999999996</v>
@@ -1292,7 +1778,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.73823000000000005</v>
@@ -1300,7 +1786,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.73823000000000005</v>
@@ -1308,7 +1794,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.69230999999999998</v>
@@ -1320,7 +1806,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.72331000000000001</v>
@@ -1328,7 +1814,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0.70665999999999995</v>
@@ -1336,7 +1822,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>0.72272999999999998</v>
@@ -1344,7 +1830,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.67393999999999998</v>
@@ -1356,7 +1842,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0.71641999999999995</v>
@@ -1364,7 +1850,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>0.73823000000000005</v>
@@ -1372,7 +1858,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.71584000000000003</v>
@@ -1384,7 +1870,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0.74339999999999995</v>
@@ -1392,7 +1878,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.74455000000000005</v>
@@ -1400,7 +1886,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.74970999999999999</v>
@@ -1408,7 +1894,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>0.59126999999999996</v>
@@ -1420,7 +1906,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>0.70952999999999999</v>
@@ -1428,7 +1914,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28">
         <v>0.70838000000000001</v>
@@ -1436,7 +1922,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.44890999999999998</v>
@@ -1448,7 +1934,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.70608000000000004</v>
@@ -1456,7 +1942,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.71182999999999996</v>
@@ -1464,7 +1950,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.78759999999999997</v>
@@ -1476,7 +1962,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.78415999999999997</v>
@@ -1484,7 +1970,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.82892999999999994</v>
@@ -1492,7 +1978,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0.78874999999999995</v>
@@ -1500,7 +1986,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.56486999999999998</v>
@@ -1512,7 +1998,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.53156999999999999</v>
@@ -1520,7 +2006,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.60275999999999996</v>
@@ -1528,7 +2014,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B39">
         <v>0.81745000000000001</v>
@@ -1540,7 +2026,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>0.79564000000000001</v>
@@ -1548,7 +2034,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.82203999999999999</v>
@@ -1556,7 +2042,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.82721</v>
@@ -1567,22 +2053,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8693EBA-F9E5-4205-8DE2-5CF3643D9239}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.73109999999999997</v>
@@ -1594,7 +2080,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.73224</v>
@@ -1602,7 +2088,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.73192999999999997</v>
@@ -1610,7 +2096,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>0.73187000000000002</v>
@@ -1618,7 +2104,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.71123000000000003</v>
@@ -1630,7 +2116,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.71386000000000005</v>
@@ -1638,7 +2124,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.72921000000000002</v>
@@ -1646,7 +2132,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.72943999999999998</v>
@@ -1654,7 +2140,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.68449000000000004</v>
@@ -1666,7 +2152,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.68955</v>
@@ -1674,7 +2160,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.62085000000000001</v>
@@ -1686,7 +2172,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.62131000000000003</v>
@@ -1694,7 +2180,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.58389000000000002</v>
@@ -1706,7 +2192,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.60921999999999998</v>
@@ -1714,7 +2200,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0.56013999999999997</v>
@@ -1726,7 +2212,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0.56925000000000003</v>
@@ -1734,7 +2220,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.56938</v>
@@ -1742,7 +2228,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.57003999999999999</v>
@@ -1750,7 +2236,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>0.63636999999999999</v>
@@ -1762,7 +2248,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>0.74827999999999995</v>
@@ -1774,7 +2260,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>0.75512999999999997</v>
@@ -1782,7 +2268,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>0.76080999999999999</v>
@@ -1790,7 +2276,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>0.55620999999999998</v>
@@ -1802,7 +2288,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>0.53607000000000005</v>
@@ -1810,7 +2296,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26">
         <v>0.72306000000000004</v>
@@ -1822,7 +2308,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27">
         <v>0.72567999999999999</v>
@@ -1830,7 +2316,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>0.72887999999999997</v>
@@ -1838,7 +2324,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0.61728000000000005</v>
@@ -1850,7 +2336,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0.61375000000000002</v>
@@ -1858,7 +2344,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>0.61621999999999999</v>
@@ -1866,7 +2352,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>0.68786000000000003</v>
@@ -1878,7 +2364,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>0.69167999999999996</v>
@@ -1886,7 +2372,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>0.70121</v>
@@ -1897,22 +2383,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5377EC-BA22-47EB-98DB-A8ABB998676D}">
   <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.98255999999999999</v>
@@ -1924,7 +2410,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.99212</v>
@@ -1932,7 +2418,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.99175999999999997</v>
@@ -1940,7 +2426,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.92906</v>
@@ -1952,7 +2438,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.99160000000000004</v>
@@ -1960,7 +2446,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.99158000000000002</v>
@@ -1968,7 +2454,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.99150000000000005</v>
@@ -1976,7 +2462,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.56969999999999998</v>
@@ -1988,7 +2474,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.59387999999999996</v>
@@ -1996,7 +2482,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.96469000000000005</v>
@@ -2004,7 +2490,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.96580999999999995</v>
@@ -2012,7 +2498,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.53820999999999997</v>
@@ -2024,7 +2510,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.96197999999999995</v>
@@ -2032,7 +2518,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.96679999999999999</v>
@@ -2040,7 +2526,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.54798999999999998</v>
@@ -2052,7 +2538,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0.55501</v>
@@ -2060,7 +2546,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>0.96167000000000002</v>
@@ -2068,7 +2554,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0.96231</v>
@@ -2076,7 +2562,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0.58098000000000005</v>
@@ -2088,7 +2574,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>0.58501000000000003</v>
@@ -2096,7 +2582,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22">
         <v>0.48826999999999998</v>
@@ -2104,7 +2590,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>0.75034000000000001</v>
@@ -2112,7 +2598,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.95779000000000003</v>
@@ -2124,7 +2610,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.96277999999999997</v>
@@ -2132,7 +2618,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.96431999999999995</v>
@@ -2140,7 +2626,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>0.95098000000000005</v>
@@ -2152,7 +2638,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28">
         <v>0.95459000000000005</v>
@@ -2160,7 +2646,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>0.97979000000000005</v>
@@ -2168,7 +2654,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.51185999999999998</v>
@@ -2180,7 +2666,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.64922000000000002</v>
@@ -2188,7 +2674,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0.67037999999999998</v>
@@ -2196,7 +2682,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>0.82213999999999998</v>
@@ -2204,7 +2690,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.74521000000000004</v>
@@ -2216,7 +2702,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0.96238999999999997</v>
@@ -2224,7 +2710,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36">
         <v>0.97790999999999995</v>
@@ -2232,7 +2718,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.51105</v>
@@ -2244,7 +2730,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.57008999999999999</v>
@@ -2252,7 +2738,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.95633000000000001</v>
@@ -2260,7 +2746,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.95711999999999997</v>
@@ -2268,7 +2754,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.95520000000000005</v>
@@ -2280,7 +2766,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.94615000000000005</v>
@@ -2288,7 +2774,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>0.94364999999999999</v>
@@ -2296,7 +2782,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B44">
         <v>0.96694999999999998</v>
@@ -2308,21 +2794,696 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.752</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.75007999999999997</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.74421000000000004</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.74339</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.74111000000000005</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.73451999999999995</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.72668999999999995</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.74175999999999997</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.66100999999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.72285999999999995</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.73153999999999997</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.73385</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.76108148973420298</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.97450000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.65234999999999999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.64398999999999995</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.61195999999999995</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.60728000000000004</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.58311999999999997</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.55315000000000003</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.52607999999999999</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.66993000000000003</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.58672999999999997</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.60218000000000005</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.59197999999999995</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.64966000000000002</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.73816609977324199</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.85409999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.81762000000000001</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.72785</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.78208</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.76607999999999998</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.78991999999999996</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.84753999999999996</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.316</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.69191999999999998</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.71584999999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.79884999999999995</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.63968999999999998</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.82015384615384601</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.99717999999999996</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.99717999999999996</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.99670999999999998</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.98028000000000004</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.96526000000000001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.96736999999999995</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.99483999999999995</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.64788999999999997</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.99717999999999996</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.99436999999999998</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.99859154929577398</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.98670000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.57347000000000004</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.56618000000000002</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.47383999999999998</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.50119000000000002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.49658000000000002</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.47960000000000003</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.51910000000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.43720999999999999</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.47666999999999998</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.53641000000000005</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.47381000000000001</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.49945000000000001</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.65000947105344398</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.92220000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.54090000000000005</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.53190999999999999</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.52542999999999995</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.50183</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.50183</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.50344999999999995</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.50726000000000004</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.53417000000000003</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.51853000000000005</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.58291999999999999</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.49569999999999997</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.55686000000000002</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.53156263209806898</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.98599999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.68383000000000005</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.66883000000000004</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.65583000000000002</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.56933</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.56138999999999994</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.56906000000000001</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.60592000000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.75566999999999995</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.55693999999999999</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.72055999999999998</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.55967</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.71682999999999997</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.70016666666666605</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.87480000000000002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.88319999999999999</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.86667000000000005</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.86504000000000003</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.83957000000000004</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.77886</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.72926999999999997</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.85799000000000003</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.74200999999999995</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.90351999999999999</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.80379</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.89539000000000002</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.88048780487804801</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.93869999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.78588000000000002</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.74856</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.80367</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.73823000000000005</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.72331000000000001</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.73823000000000005</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.74970999999999999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.70952999999999999</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.71182999999999996</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.82892999999999994</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.60275999999999996</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.82721</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.78473019517795595</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.93610000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.73224</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.72943999999999998</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.68955</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.62131000000000003</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.60921999999999998</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.57003999999999999</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.63636999999999999</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.76080999999999999</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.55620999999999998</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.72887999999999997</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.61728000000000005</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.70121</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.73591417910447698</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.99212</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.96580999999999995</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.96679999999999999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.96231</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.75034000000000001</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.96431999999999995</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.97979000000000005</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.82213999999999998</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.97790999999999995</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.95711999999999997</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.96694999999999998</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.98260560519902496</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.97860000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <f>AVERAGE(B3:B13)</f>
+        <v>0.76385363636363646</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" ref="C14:M14" si="0">AVERAGE(C3:C13)</f>
+        <v>0.74898363636363641</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.73779636363636358</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.71585272727272731</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.7080581818181817</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.68091363636363633</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.70191727272727278</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.70524545454545462</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.63380727272727266</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.75610909090909084</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.69330909090909087</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.74376999999999993</v>
+      </c>
+      <c r="N14" s="2">
+        <f>AVERAGE(N3:N13)</f>
+        <v>0.7803154126486137</v>
+      </c>
+      <c r="O14" s="2">
+        <f>AVERAGE(O3:O13)</f>
+        <v>0.93570909090909093</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="N1:O1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B1:N1048576">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>B1=MAX($B1:$N1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>B3=MAX($B3:$N3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814B012A-D937-47C4-8AC9-6A6E5FDF72BE}">
   <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.74761</v>
@@ -2330,7 +3491,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.75158000000000003</v>
@@ -2338,7 +3499,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.75205</v>
@@ -2350,7 +3511,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>0.74997999999999998</v>
@@ -2358,7 +3519,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.74456999999999995</v>
@@ -2366,7 +3527,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.74836999999999998</v>
@@ -2374,7 +3535,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.75007999999999997</v>
@@ -2386,7 +3547,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.75007999999999997</v>
@@ -2394,7 +3555,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.71584000000000003</v>
@@ -2402,7 +3563,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.72428000000000003</v>
@@ -2410,7 +3571,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.74421000000000004</v>
@@ -2422,7 +3583,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.74414999999999998</v>
@@ -2430,7 +3591,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.71930000000000005</v>
@@ -2438,7 +3599,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.73812</v>
@@ -2446,7 +3607,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.74339</v>
@@ -2458,7 +3619,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.74319999999999997</v>
@@ -2466,7 +3627,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>0.71847000000000005</v>
@@ -2474,7 +3635,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0.73836000000000002</v>
@@ -2482,7 +3643,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.74111000000000005</v>
@@ -2494,7 +3655,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0.74097000000000002</v>
@@ -2502,7 +3663,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22">
         <v>0.71986000000000006</v>
@@ -2510,7 +3671,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>0.71870999999999996</v>
@@ -2522,7 +3683,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>0.73451999999999995</v>
@@ -2530,7 +3691,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.71862999999999999</v>
@@ -2542,7 +3703,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.72275999999999996</v>
@@ -2550,7 +3711,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>0.72668999999999995</v>
@@ -2558,7 +3719,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28">
         <v>0.73404000000000003</v>
@@ -2570,7 +3731,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>0.74175999999999997</v>
@@ -2578,7 +3739,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.65053000000000005</v>
@@ -2590,7 +3751,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.66100999999999999</v>
@@ -2598,7 +3759,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.71103000000000005</v>
@@ -2606,7 +3767,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.70535999999999999</v>
@@ -2618,7 +3779,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.72285999999999995</v>
@@ -2626,7 +3787,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0.70821999999999996</v>
@@ -2634,7 +3795,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.73038000000000003</v>
@@ -2646,7 +3807,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.73038000000000003</v>
@@ -2654,7 +3815,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.73153999999999997</v>
@@ -2662,7 +3823,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B39">
         <v>0.71160000000000001</v>
@@ -2674,7 +3835,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>0.72340000000000004</v>
@@ -2682,7 +3843,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.73385</v>
@@ -2690,7 +3851,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.72958999999999996</v>
@@ -2702,22 +3863,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96173FC3-F951-424B-A654-7BA719E64DFA}">
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.64753000000000005</v>
@@ -2725,7 +3886,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.65234999999999999</v>
@@ -2737,7 +3898,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.63349999999999995</v>
@@ -2745,7 +3906,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.64115999999999995</v>
@@ -2753,7 +3914,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.64398999999999995</v>
@@ -2765,7 +3926,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0.59609000000000001</v>
@@ -2777,7 +3938,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.61195999999999995</v>
@@ -2785,7 +3946,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.60189999999999999</v>
@@ -2793,7 +3954,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.46357999999999999</v>
@@ -2801,7 +3962,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.60346</v>
@@ -2813,7 +3974,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.60643000000000002</v>
@@ -2821,7 +3982,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.60728000000000004</v>
@@ -2829,7 +3990,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.46994999999999998</v>
@@ -2841,7 +4002,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.56738999999999995</v>
@@ -2849,7 +4010,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.58311999999999997</v>
@@ -2857,7 +4018,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0.57865999999999995</v>
@@ -2865,7 +4026,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.51558999999999999</v>
@@ -2877,7 +4038,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.54052999999999995</v>
@@ -2885,7 +4046,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0.55315000000000003</v>
@@ -2893,7 +4054,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0.52388000000000001</v>
@@ -2905,7 +4066,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.52607999999999999</v>
@@ -2913,7 +4074,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0.51651000000000002</v>
@@ -2921,7 +4082,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24">
         <v>0.65505000000000002</v>
@@ -2933,7 +4094,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>0.66908000000000001</v>
@@ -2941,7 +4102,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>0.66993000000000003</v>
@@ -2949,7 +4110,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>0.64881</v>
@@ -2957,7 +4118,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>0.52622000000000002</v>
@@ -2969,7 +4130,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.57808999999999999</v>
@@ -2977,7 +4138,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.58672999999999997</v>
@@ -2985,7 +4146,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.58574000000000004</v>
@@ -2993,7 +4154,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.60218000000000005</v>
@@ -3005,7 +4166,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.40178999999999998</v>
@@ -3013,7 +4174,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.49008000000000002</v>
@@ -3021,7 +4182,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B35">
         <v>0.56589999999999996</v>
@@ -3033,7 +4194,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.59197999999999995</v>
@@ -3041,7 +4202,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.58248</v>
@@ -3049,7 +4210,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.58389999999999997</v>
@@ -3057,7 +4218,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B39">
         <v>0.60919999999999996</v>
@@ -3069,7 +4230,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>0.58687999999999996</v>
@@ -3077,7 +4238,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.64966000000000002</v>
@@ -3085,7 +4246,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.64753000000000005</v>
@@ -3096,22 +4257,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFC0E0F-6E6F-42A6-8CF4-86ECBE8FE863}">
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.44827</v>
@@ -3123,7 +4284,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.81762000000000001</v>
@@ -3131,7 +4292,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.63468999999999998</v>
@@ -3139,7 +4300,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.30153999999999997</v>
@@ -3151,7 +4312,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.72785</v>
@@ -3159,7 +4320,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0.43808000000000002</v>
@@ -3171,7 +4332,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.78208</v>
@@ -3179,7 +4340,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.72138000000000002</v>
@@ -3187,7 +4348,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.72423000000000004</v>
@@ -3195,7 +4356,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.50885000000000002</v>
@@ -3207,7 +4368,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.76276999999999995</v>
@@ -3215,7 +4376,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.76607999999999998</v>
@@ -3223,7 +4384,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.50876999999999994</v>
@@ -3235,7 +4396,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.78991999999999996</v>
@@ -3243,7 +4404,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.76131000000000004</v>
@@ -3251,7 +4412,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0.76400000000000001</v>
@@ -3259,7 +4420,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.50585000000000002</v>
@@ -3271,7 +4432,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.35654000000000002</v>
@@ -3279,7 +4440,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0.84462000000000004</v>
@@ -3287,7 +4448,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>0.84753999999999996</v>
@@ -3295,7 +4456,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.61223000000000005</v>
@@ -3307,7 +4468,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0.78900000000000003</v>
@@ -3315,7 +4476,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.77712000000000003</v>
@@ -3323,7 +4484,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>0.316</v>
@@ -3335,7 +4496,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>0.27792</v>
@@ -3343,7 +4504,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>0.26430999999999999</v>
@@ -3351,7 +4512,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>0.69191999999999998</v>
@@ -3363,7 +4524,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.62185000000000001</v>
@@ -3371,7 +4532,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.65207999999999999</v>
@@ -3379,7 +4540,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.66554000000000002</v>
@@ -3387,7 +4548,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.41685</v>
@@ -3399,7 +4560,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.71584999999999999</v>
@@ -3407,7 +4568,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.67945999999999995</v>
@@ -3415,7 +4576,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0.69762000000000002</v>
@@ -3423,7 +4584,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.48437999999999998</v>
@@ -3435,7 +4596,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.79884999999999995</v>
@@ -3443,7 +4604,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.79408000000000001</v>
@@ -3451,7 +4612,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B39">
         <v>0.50680999999999998</v>
@@ -3463,7 +4624,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>0.46515000000000001</v>
@@ -3471,7 +4632,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.38338</v>
@@ -3479,7 +4640,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.63968999999999998</v>
@@ -3490,22 +4651,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF3F352-3EF6-4C40-860C-2F33291BDFA8}">
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.99577000000000004</v>
@@ -3517,7 +4678,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.99717999999999996</v>
@@ -3525,7 +4686,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0.99155000000000004</v>
@@ -3537,7 +4698,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.99436999999999998</v>
@@ -3545,7 +4706,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.99717999999999996</v>
@@ -3553,7 +4714,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0.99248999999999998</v>
@@ -3565,7 +4726,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.99531000000000003</v>
@@ -3573,7 +4734,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.99670999999999998</v>
@@ -3581,7 +4742,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0.99295999999999995</v>
@@ -3593,7 +4754,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.99390000000000001</v>
@@ -3601,7 +4762,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>0.97840000000000005</v>
@@ -3613,7 +4774,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>0.97887000000000002</v>
@@ -3621,7 +4782,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.98028000000000004</v>
@@ -3629,7 +4790,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0.95728000000000002</v>
@@ -3641,7 +4802,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0.96338000000000001</v>
@@ -3649,7 +4810,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0.96526000000000001</v>
@@ -3657,7 +4818,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>0.95962000000000003</v>
@@ -3669,7 +4830,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>0.96103000000000005</v>
@@ -3677,7 +4838,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>0.96736999999999995</v>
@@ -3685,7 +4846,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>0.99343000000000004</v>
@@ -3697,7 +4858,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>0.99436999999999998</v>
@@ -3705,7 +4866,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>0.99483999999999995</v>
@@ -3713,7 +4874,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>0.64788999999999997</v>
@@ -3725,7 +4886,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>0.6169</v>
@@ -3733,7 +4894,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>0.62770000000000004</v>
@@ -3741,7 +4902,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>0.55586999999999998</v>
@@ -3749,7 +4910,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>0.99060999999999999</v>
@@ -3761,7 +4922,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29">
         <v>0.99624000000000001</v>
@@ -3769,7 +4930,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0.99717999999999996</v>
@@ -3777,7 +4938,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>0.99390000000000001</v>
@@ -3789,7 +4950,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>0.99436999999999998</v>
@@ -3801,7 +4962,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>0.99202000000000001</v>
@@ -3812,22 +4973,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A4D3B8-EA7D-4BBD-950A-F6390B43B165}">
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.55615000000000003</v>
@@ -3839,7 +5000,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.56925999999999999</v>
@@ -3847,7 +5008,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.57174000000000003</v>
@@ -3855,7 +5016,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>0.57347000000000004</v>
@@ -3863,7 +5024,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.55745</v>
@@ -3875,7 +5036,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.56489999999999996</v>
@@ -3883,7 +5044,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.56618000000000002</v>
@@ -3891,7 +5052,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.47383999999999998</v>
@@ -3903,7 +5064,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.46977000000000002</v>
@@ -3911,7 +5072,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.44077</v>
@@ -3919,7 +5080,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.50119000000000002</v>
@@ -3931,7 +5092,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.41348000000000001</v>
@@ -3939,7 +5100,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.48381000000000002</v>
@@ -3951,7 +5112,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.49658000000000002</v>
@@ -3959,7 +5120,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0.46695999999999999</v>
@@ -3971,7 +5132,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0.47960000000000003</v>
@@ -3979,7 +5140,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.47815000000000002</v>
@@ -3987,7 +5148,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.42636000000000002</v>
@@ -3995,7 +5156,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>0.51495000000000002</v>
@@ -4007,7 +5168,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0.51861999999999997</v>
@@ -4015,7 +5176,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.51910000000000001</v>
@@ -4023,7 +5184,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0.51822000000000001</v>
@@ -4031,7 +5192,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24">
         <v>0.43720999999999999</v>
@@ -4043,7 +5204,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>0.42781999999999998</v>
@@ -4051,7 +5212,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>0.45831</v>
@@ -4063,7 +5224,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>0.41425000000000001</v>
@@ -4071,7 +5232,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>0.47589999999999999</v>
@@ -4079,7 +5240,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.47666999999999998</v>
@@ -4087,7 +5248,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0.48171000000000003</v>
@@ -4099,7 +5260,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31">
         <v>0.48127999999999999</v>
@@ -4107,7 +5268,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.53117999999999999</v>
@@ -4115,7 +5276,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.53641000000000005</v>
@@ -4123,7 +5284,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B34">
         <v>0.47381000000000001</v>
@@ -4135,7 +5296,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B35">
         <v>0.47099000000000002</v>
@@ -4143,7 +5304,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.44855</v>
@@ -4151,7 +5312,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B37">
         <v>0.48259000000000002</v>
@@ -4163,7 +5324,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B38">
         <v>0.49945000000000001</v>
@@ -4174,22 +5335,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8B5A3-CE5B-4A8C-9C85-AF312DF32E51}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.54093000000000002</v>
@@ -4201,7 +5362,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.50585000000000002</v>
@@ -4209,7 +5370,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0.51951999999999998</v>
@@ -4221,7 +5382,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.53190999999999999</v>
@@ -4229,7 +5390,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.52966000000000002</v>
@@ -4237,7 +5398,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.52924000000000004</v>
@@ -4245,7 +5406,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0.52049999999999996</v>
@@ -4257,7 +5418,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.52542999999999995</v>
@@ -4265,7 +5426,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.52431000000000005</v>
@@ -4273,7 +5434,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.50183</v>
@@ -4285,7 +5446,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.46189000000000002</v>
@@ -4293,7 +5454,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.49682999999999999</v>
@@ -4301,7 +5462,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.50183</v>
@@ -4313,7 +5474,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.47619</v>
@@ -4321,7 +5482,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.49084</v>
@@ -4329,7 +5490,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0.50007000000000001</v>
@@ -4341,7 +5502,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.50344999999999995</v>
@@ -4349,7 +5510,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>0.50726000000000004</v>
@@ -4361,7 +5522,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>0.48048000000000002</v>
@@ -4369,7 +5530,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>0.52669999999999995</v>
@@ -4381,7 +5542,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>0.53036000000000005</v>
@@ -4389,7 +5550,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>0.53417000000000003</v>
@@ -4397,7 +5558,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>0.51853000000000005</v>
@@ -4409,7 +5570,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>0.51726000000000005</v>
@@ -4417,7 +5578,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>0.49556</v>
@@ -4425,7 +5586,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27">
         <v>0.53205999999999998</v>
@@ -4437,7 +5598,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>0.56559000000000004</v>
@@ -4445,7 +5606,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29">
         <v>0.58291999999999999</v>
@@ -4453,7 +5614,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0.48837999999999998</v>
@@ -4465,7 +5626,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>0.47089999999999999</v>
@@ -4473,7 +5634,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>0.49569999999999997</v>
@@ -4481,7 +5642,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>0.54615000000000002</v>
@@ -4493,7 +5654,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>0.55318999999999996</v>
@@ -4501,7 +5662,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B35">
         <v>0.55686000000000002</v>
@@ -4512,22 +5673,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B796E0-256A-4A27-9A69-9963FBE3B123}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.68010999999999999</v>
@@ -4539,7 +5700,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0.68383000000000005</v>
@@ -4547,7 +5708,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0.67630999999999997</v>
@@ -4555,7 +5716,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>0.68213999999999997</v>
@@ -4563,7 +5724,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0.66056000000000004</v>
@@ -4575,7 +5736,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.66861000000000004</v>
@@ -4583,7 +5744,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.66883000000000004</v>
@@ -4591,7 +5752,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0.62133000000000005</v>
@@ -4603,7 +5764,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.65583000000000002</v>
@@ -4611,7 +5772,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.54978000000000005</v>
@@ -4623,7 +5784,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.56760999999999995</v>
@@ -4631,7 +5792,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.56933</v>
@@ -4639,7 +5800,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.48764000000000002</v>
@@ -4651,7 +5812,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.54483000000000004</v>
@@ -4659,7 +5820,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0.54805999999999999</v>
@@ -4667,7 +5828,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>0.56138999999999994</v>
@@ -4675,7 +5836,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.48566999999999999</v>
@@ -4687,7 +5848,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0.56521999999999994</v>
@@ -4695,7 +5856,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0.56906000000000001</v>
@@ -4703,7 +5864,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0.58743999999999996</v>
@@ -4715,7 +5876,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.60592000000000001</v>
@@ -4723,7 +5884,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>0.60472000000000004</v>
@@ -4731,7 +5892,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.59699999999999998</v>
@@ -4739,7 +5900,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>0.74978</v>
@@ -4751,7 +5912,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>0.75217000000000001</v>
@@ -4759,7 +5920,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>0.75566999999999995</v>
@@ -4767,7 +5928,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>0.52010999999999996</v>
@@ -4779,7 +5940,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.54117000000000004</v>
@@ -4787,7 +5948,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.55393999999999999</v>
@@ -4795,7 +5956,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.55693999999999999</v>
@@ -4803,7 +5964,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0.66439000000000004</v>
@@ -4815,7 +5976,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0.71494000000000002</v>
@@ -4823,7 +5984,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0.72055999999999998</v>
@@ -4831,7 +5992,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0.70011000000000001</v>
@@ -4839,7 +6000,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.54471999999999998</v>
@@ -4851,7 +6012,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.55967</v>
@@ -4859,7 +6020,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.54881000000000002</v>
@@ -4867,7 +6028,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.55528</v>
@@ -4875,7 +6036,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>0.70977999999999997</v>
@@ -4887,7 +6048,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>0.71150000000000002</v>
@@ -4895,7 +6056,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0.71011000000000002</v>
@@ -4903,364 +6064,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>0.71682999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F9DFA3-0E78-460F-9480-3FC988D2C4F5}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
-        <v>0.84877999999999998</v>
-      </c>
-      <c r="C2">
-        <f>MAX(B2:B4)</f>
-        <v>0.87480000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>0.86938000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>0.87480000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5">
-        <v>0.88319999999999999</v>
-      </c>
-      <c r="C5">
-        <f>MAX(B5:B6)</f>
-        <v>0.88319999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>0.86775000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>0.67642000000000002</v>
-      </c>
-      <c r="C7">
-        <f>MAX(B7:B9)</f>
-        <v>0.86667000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8">
-        <v>0.58808000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>0.86667000000000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10">
-        <v>0.64173000000000002</v>
-      </c>
-      <c r="C10">
-        <f>MAX(B10:B11)</f>
-        <v>0.86504000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11">
-        <v>0.86504000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
-        <v>0.67317000000000005</v>
-      </c>
-      <c r="C12">
-        <f>MAX(B12:B14)</f>
-        <v>0.83957000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13">
-        <v>0.61761999999999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14">
-        <v>0.83957000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>0.58699000000000001</v>
-      </c>
-      <c r="C15">
-        <f>MAX(B15:B17)</f>
-        <v>0.77886</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0.73333000000000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>0.77886</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18">
-        <v>0.5393</v>
-      </c>
-      <c r="C18">
-        <f>MAX(B18:B21)</f>
-        <v>0.72926999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19">
-        <v>0.55501</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20">
-        <v>0.72926999999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21">
-        <v>0.71220000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22">
-        <v>0.78861999999999999</v>
-      </c>
-      <c r="C22">
-        <f>MAX(B22:B24)</f>
-        <v>0.85799000000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <v>0.84714999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24">
-        <v>0.85799000000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25">
-        <v>0.50678000000000001</v>
-      </c>
-      <c r="C25">
-        <f>MAX(B25:B27)</f>
-        <v>0.74200999999999995</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26">
-        <v>0.71762000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27">
-        <v>0.74200999999999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28">
-        <v>0.65256999999999998</v>
-      </c>
-      <c r="C28">
-        <f>MAX(B28:B31)</f>
-        <v>0.90351999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29">
-        <v>0.60487999999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30">
-        <v>0.62385000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31">
-        <v>0.90351999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32">
-        <v>0.69621</v>
-      </c>
-      <c r="C32">
-        <f>MAX(B32:B34)</f>
-        <v>0.80379</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33">
-        <v>0.74958999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34">
-        <v>0.80379</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
-        <v>0.61680000000000001</v>
-      </c>
-      <c r="C35">
-        <f>MAX(B35:B37)</f>
-        <v>0.89539000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
-        <v>0.87858999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
-        <v>0.89539000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5B9A97-411B-4AA5-B419-D33A02599AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90019CA3-3666-4298-9BFB-5BF06FD0A168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="38">
   <si>
     <t>Arrhy</t>
   </si>
@@ -206,6 +206,9 @@
   <si>
     <t>Arrhythmia</t>
   </si>
+  <si>
+    <t>Skewness</t>
+  </si>
 </sst>
 </file>
 
@@ -213,8 +216,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -272,57 +275,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -611,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -1294,9 +1262,114 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6">
+        <v>2.0370831182289302</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3.1547216312678601</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="6">
+        <v>9.8845764865245496</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="6">
+        <v>3.5183738979013799</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="6">
+        <v>3.2411972220237102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1.8064453738353601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="6">
+        <v>0.81389733258028796</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6">
+        <v>2.7273997511512502</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="6">
+        <v>0.39759268151465099</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1.26708352406697</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1.95101294625013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="6">
+        <f>AVERAGE(B20:B30)</f>
+        <v>2.799943996849553</v>
       </c>
     </row>
   </sheetData>
@@ -2795,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -3449,22 +3522,99 @@
         <v>0.93570909090909093</v>
       </c>
     </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" t="str">
+        <f>_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B3:N3),"]")</f>
+        <v>[0.752,0.75008,0.74421,0.74339,0.74111,0.73452,0.72669,0.74176,0.66101,0.72286,0.73154,0.73385,0.761081489734203]</v>
+      </c>
+      <c r="M18" t="str">
+        <f>_xlfn.TEXTJOIN("','",TRUE,A3:A13)</f>
+        <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hep','Pima','PenDigits</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" t="str">
+        <f t="shared" ref="B19:B28" si="1">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
+        <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242]</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846]</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774]</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444]</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069]</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048]</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956]</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477]</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" t="str">
+        <f t="shared" si="1"/>
+        <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025]</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B31" t="str">
+        <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
+        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma AUC</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:N1048576">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>B1=MAX($B1:$N1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90019CA3-3666-4298-9BFB-5BF06FD0A168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4EBCA5-33E2-4615-B118-0418F7137231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="38">
   <si>
     <t>Arrhy</t>
   </si>
@@ -133,9 +133,6 @@
     </r>
   </si>
   <si>
-    <t>Gamma AUC</t>
-  </si>
-  <si>
     <t>Algorithm</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   <si>
     <t>Skewness</t>
   </si>
+  <si>
+    <t>Gamma ROC AUC</t>
+  </si>
 </sst>
 </file>
 
@@ -271,24 +271,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -609,37 +612,37 @@
         <v>13</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
       </c>
       <c r="J1" t="s">
         <v>15</v>
       </c>
       <c r="K1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s">
         <v>14</v>
       </c>
       <c r="M1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N1" t="s">
         <v>16</v>
       </c>
       <c r="O1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" t="s">
         <v>29</v>
-      </c>
-      <c r="P1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1194,7 +1197,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <f>AVERAGE(B2:B12)</f>
@@ -1259,7 +1262,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1272,14 +1275,14 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="6">
+        <v>35</v>
+      </c>
+      <c r="B20" s="5">
         <v>2.0370831182289302</v>
       </c>
     </row>
@@ -1287,7 +1290,7 @@
       <c r="A21" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>3.1547216312678601</v>
       </c>
     </row>
@@ -1295,7 +1298,7 @@
       <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>9.8845764865245496</v>
       </c>
     </row>
@@ -1303,7 +1306,7 @@
       <c r="A23" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>3.5183738979013799</v>
       </c>
     </row>
@@ -1311,7 +1314,7 @@
       <c r="A24" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>3.2411972220237102</v>
       </c>
     </row>
@@ -1319,7 +1322,7 @@
       <c r="A25" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>1.8064453738353601</v>
       </c>
     </row>
@@ -1327,7 +1330,7 @@
       <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>0.81389733258028796</v>
       </c>
     </row>
@@ -1335,7 +1338,7 @@
       <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>2.7273997511512502</v>
       </c>
     </row>
@@ -1343,7 +1346,7 @@
       <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>0.39759268151465099</v>
       </c>
     </row>
@@ -1351,7 +1354,7 @@
       <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>1.26708352406697</v>
       </c>
     </row>
@@ -1359,15 +1362,15 @@
       <c r="A30" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>1.95101294625013</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5">
         <f>AVERAGE(B20:B30)</f>
         <v>2.799943996849553</v>
       </c>
@@ -1385,10 +1388,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1421,7 +1424,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.88319999999999999</v>
@@ -1433,7 +1436,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.86775000000000002</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.67642000000000002</v>
@@ -1453,7 +1456,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.58808000000000005</v>
@@ -1461,7 +1464,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.86667000000000005</v>
@@ -1469,7 +1472,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.64173000000000002</v>
@@ -1481,7 +1484,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.86504000000000003</v>
@@ -1489,7 +1492,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.67317000000000005</v>
@@ -1501,7 +1504,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.61761999999999995</v>
@@ -1509,7 +1512,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.83957000000000004</v>
@@ -1545,7 +1548,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>0.5393</v>
@@ -1557,7 +1560,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0.55501</v>
@@ -1565,7 +1568,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.72926999999999997</v>
@@ -1573,7 +1576,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0.71220000000000006</v>
@@ -1609,7 +1612,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.50678000000000001</v>
@@ -1621,7 +1624,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.71762000000000004</v>
@@ -1629,7 +1632,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>0.74200999999999995</v>
@@ -1673,7 +1676,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0.69621</v>
@@ -1685,7 +1688,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>0.74958999999999998</v>
@@ -1693,7 +1696,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>0.80379</v>
@@ -1701,7 +1704,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35">
         <v>0.61680000000000001</v>
@@ -1713,7 +1716,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>0.87858999999999998</v>
@@ -1721,7 +1724,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.89539000000000002</v>
@@ -1739,10 +1742,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1775,7 +1778,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.69116</v>
@@ -1787,7 +1790,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.74856</v>
@@ -1795,7 +1798,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.74168000000000001</v>
@@ -1803,7 +1806,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.76693</v>
@@ -1815,7 +1818,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.80023</v>
@@ -1823,7 +1826,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.80367</v>
@@ -1831,7 +1834,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.72789999999999999</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.73363999999999996</v>
@@ -1851,7 +1854,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.73823000000000005</v>
@@ -1859,7 +1862,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0.73823000000000005</v>
@@ -1867,7 +1870,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.69230999999999998</v>
@@ -1879,7 +1882,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.72331000000000001</v>
@@ -1887,7 +1890,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.70665999999999995</v>
@@ -1895,7 +1898,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>0.72272999999999998</v>
@@ -1931,7 +1934,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0.71584000000000003</v>
@@ -1943,7 +1946,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0.74339999999999995</v>
@@ -1951,7 +1954,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>0.74455000000000005</v>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>0.74970999999999999</v>
@@ -1995,7 +1998,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>0.44890999999999998</v>
@@ -2007,7 +2010,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.70608000000000004</v>
@@ -2015,7 +2018,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.71182999999999996</v>
@@ -2059,7 +2062,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.56486999999999998</v>
@@ -2071,7 +2074,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.53156999999999999</v>
@@ -2079,7 +2082,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.60275999999999996</v>
@@ -2087,7 +2090,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.81745000000000001</v>
@@ -2099,7 +2102,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.79564000000000001</v>
@@ -2107,7 +2110,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.82203999999999999</v>
@@ -2115,7 +2118,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.82721</v>
@@ -2133,10 +2136,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2177,7 +2180,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.71123000000000003</v>
@@ -2189,7 +2192,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.71386000000000005</v>
@@ -2197,7 +2200,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0.72921000000000002</v>
@@ -2205,7 +2208,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>0.72943999999999998</v>
@@ -2213,7 +2216,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.68449000000000004</v>
@@ -2225,7 +2228,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.68955</v>
@@ -2233,7 +2236,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.62085000000000001</v>
@@ -2245,7 +2248,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.62131000000000003</v>
@@ -2253,7 +2256,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.58389000000000002</v>
@@ -2265,7 +2268,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.60921999999999998</v>
@@ -2309,7 +2312,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.63636999999999999</v>
@@ -2349,7 +2352,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.55620999999999998</v>
@@ -2361,7 +2364,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.53607000000000005</v>
@@ -2397,7 +2400,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0.61728000000000005</v>
@@ -2409,7 +2412,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.61375000000000002</v>
@@ -2417,7 +2420,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.61621999999999999</v>
@@ -2425,7 +2428,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>0.68786000000000003</v>
@@ -2437,7 +2440,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>0.69167999999999996</v>
@@ -2445,7 +2448,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34">
         <v>0.70121</v>
@@ -2463,10 +2466,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2499,7 +2502,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.92906</v>
@@ -2511,7 +2514,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.99160000000000004</v>
@@ -2519,7 +2522,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.99158000000000002</v>
@@ -2527,7 +2530,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0.99150000000000005</v>
@@ -2535,7 +2538,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.56969999999999998</v>
@@ -2547,7 +2550,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.59387999999999996</v>
@@ -2555,7 +2558,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.96469000000000005</v>
@@ -2563,7 +2566,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0.96580999999999995</v>
@@ -2571,7 +2574,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.53820999999999997</v>
@@ -2583,7 +2586,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0.96197999999999995</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0.96679999999999999</v>
@@ -2599,7 +2602,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.54798999999999998</v>
@@ -2611,7 +2614,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.55501</v>
@@ -2619,7 +2622,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>0.96167000000000002</v>
@@ -2627,7 +2630,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>0.96231</v>
@@ -2671,7 +2674,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>0.95779000000000003</v>
@@ -2683,7 +2686,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>0.96277999999999997</v>
@@ -2691,7 +2694,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>0.96431999999999995</v>
@@ -2727,7 +2730,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.51185999999999998</v>
@@ -2739,7 +2742,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.64922000000000002</v>
@@ -2747,7 +2750,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32">
         <v>0.67037999999999998</v>
@@ -2755,7 +2758,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>0.82213999999999998</v>
@@ -2791,7 +2794,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.51105</v>
@@ -2803,7 +2806,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.57008999999999999</v>
@@ -2811,7 +2814,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>0.95633000000000001</v>
@@ -2819,7 +2822,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B40">
         <v>0.95711999999999997</v>
@@ -2827,7 +2830,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.95520000000000005</v>
@@ -2839,7 +2842,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.94615000000000005</v>
@@ -2847,7 +2850,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43">
         <v>0.94364999999999999</v>
@@ -2855,7 +2858,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44">
         <v>0.96694999999999998</v>
@@ -2868,34 +2871,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="5"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2905,48 +2909,48 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="N2" s="4" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1">
         <v>0.752</v>
@@ -3463,7 +3467,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2">
         <f>AVERAGE(B3:B13)</f>
@@ -3522,7 +3526,7 @@
         <v>0.93570909090909093</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B3:N3),"]")</f>
         <v>[0.752,0.75008,0.74421,0.74339,0.74111,0.73452,0.72669,0.74176,0.66101,0.72286,0.73154,0.73385,0.761081489734203]</v>
@@ -3532,70 +3536,179 @@
         <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hep','Pima','PenDigits</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f t="shared" ref="B19:B28" si="1">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
         <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242]</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846]</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774]</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444]</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069]</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" t="str">
         <f t="shared" si="1"/>
         <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
       </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="7">
+        <f>N8-K8</f>
+        <v>-5.1357367901931017E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f t="shared" si="1"/>
         <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048]</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956]</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477]</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025]</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
-        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma AUC</v>
+        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma ROC AUC</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.97450000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.85409999999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.98670000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.92220000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.98599999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.93869999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.93610000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.97860000000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="2">
+        <f>AVERAGE(B34:B44)</f>
+        <v>0.93570909090909093</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +3716,7 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:N1048576">
+  <conditionalFormatting sqref="B1:N32 B46:N1048576 C33:N45">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>B1=MAX($B1:$N1)</formula>
     </cfRule>
@@ -3625,10 +3738,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3669,7 +3782,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.74456999999999995</v>
@@ -3677,7 +3790,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.74836999999999998</v>
@@ -3685,7 +3798,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0.75007999999999997</v>
@@ -3697,7 +3810,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>0.75007999999999997</v>
@@ -3705,7 +3818,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.71584000000000003</v>
@@ -3713,7 +3826,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.72428000000000003</v>
@@ -3721,7 +3834,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0.74421000000000004</v>
@@ -3733,7 +3846,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>0.74414999999999998</v>
@@ -3741,7 +3854,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0.71930000000000005</v>
@@ -3749,7 +3862,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0.73812</v>
@@ -3757,7 +3870,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>0.74339</v>
@@ -3769,7 +3882,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>0.74319999999999997</v>
@@ -3777,7 +3890,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>0.71847000000000005</v>
@@ -3785,7 +3898,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>0.73836000000000002</v>
@@ -3793,7 +3906,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>0.74111000000000005</v>
@@ -3805,7 +3918,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>0.74097000000000002</v>
@@ -3841,7 +3954,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>0.71862999999999999</v>
@@ -3853,7 +3966,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>0.72275999999999996</v>
@@ -3861,7 +3974,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>0.72668999999999995</v>
@@ -3889,7 +4002,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.65053000000000005</v>
@@ -3901,7 +4014,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.66100999999999999</v>
@@ -3945,7 +4058,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.73038000000000003</v>
@@ -3957,7 +4070,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.73038000000000003</v>
@@ -3965,7 +4078,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.73153999999999997</v>
@@ -3973,7 +4086,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.71160000000000001</v>
@@ -3985,7 +4098,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.72340000000000004</v>
@@ -3993,7 +4106,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.73385</v>
@@ -4001,7 +4114,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.72958999999999996</v>
@@ -4020,10 +4133,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4056,7 +4169,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.64115999999999995</v>
@@ -4064,7 +4177,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.64398999999999995</v>
@@ -4076,7 +4189,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.59609000000000001</v>
@@ -4088,7 +4201,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.61195999999999995</v>
@@ -4096,7 +4209,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.60189999999999999</v>
@@ -4104,7 +4217,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.46357999999999999</v>
@@ -4112,7 +4225,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.60346</v>
@@ -4124,7 +4237,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.60643000000000002</v>
@@ -4132,7 +4245,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.60728000000000004</v>
@@ -4140,7 +4253,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.46994999999999998</v>
@@ -4152,7 +4265,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.56738999999999995</v>
@@ -4160,7 +4273,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.58311999999999997</v>
@@ -4168,7 +4281,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.57865999999999995</v>
@@ -4204,7 +4317,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0.52388000000000001</v>
@@ -4216,7 +4329,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0.52607999999999999</v>
@@ -4224,7 +4337,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0.51651000000000002</v>
@@ -4268,7 +4381,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>0.52622000000000002</v>
@@ -4280,7 +4393,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>0.57808999999999999</v>
@@ -4288,7 +4401,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.58672999999999997</v>
@@ -4296,7 +4409,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.58574000000000004</v>
@@ -4332,7 +4445,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>0.56589999999999996</v>
@@ -4344,7 +4457,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.59197999999999995</v>
@@ -4352,7 +4465,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.58248</v>
@@ -4360,7 +4473,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.58389999999999997</v>
@@ -4368,7 +4481,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.60919999999999996</v>
@@ -4380,7 +4493,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.58687999999999996</v>
@@ -4388,7 +4501,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.64966000000000002</v>
@@ -4396,7 +4509,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.64753000000000005</v>
@@ -4414,10 +4527,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4450,7 +4563,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.30153999999999997</v>
@@ -4462,7 +4575,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.72785</v>
@@ -4470,7 +4583,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.43808000000000002</v>
@@ -4482,7 +4595,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.78208</v>
@@ -4490,7 +4603,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.72138000000000002</v>
@@ -4498,7 +4611,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.72423000000000004</v>
@@ -4506,7 +4619,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.50885000000000002</v>
@@ -4518,7 +4631,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.76276999999999995</v>
@@ -4526,7 +4639,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.76607999999999998</v>
@@ -4534,7 +4647,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.50876999999999994</v>
@@ -4546,7 +4659,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.78991999999999996</v>
@@ -4554,7 +4667,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.76131000000000004</v>
@@ -4562,7 +4675,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.76400000000000001</v>
@@ -4606,7 +4719,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0.61223000000000005</v>
@@ -4618,7 +4731,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0.78900000000000003</v>
@@ -4626,7 +4739,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>0.77712000000000003</v>
@@ -4662,7 +4775,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>0.69191999999999998</v>
@@ -4674,7 +4787,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>0.62185000000000001</v>
@@ -4682,7 +4795,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.65207999999999999</v>
@@ -4690,7 +4803,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.66554000000000002</v>
@@ -4734,7 +4847,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.48437999999999998</v>
@@ -4746,7 +4859,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.79884999999999995</v>
@@ -4754,7 +4867,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.79408000000000001</v>
@@ -4762,7 +4875,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>0.50680999999999998</v>
@@ -4774,7 +4887,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.46515000000000001</v>
@@ -4782,7 +4895,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.38338</v>
@@ -4790,7 +4903,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.63968999999999998</v>
@@ -4808,10 +4921,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4836,7 +4949,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0.99155000000000004</v>
@@ -4848,7 +4961,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.99436999999999998</v>
@@ -4856,7 +4969,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.99717999999999996</v>
@@ -4864,7 +4977,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0.99248999999999998</v>
@@ -4876,7 +4989,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.99531000000000003</v>
@@ -4884,7 +4997,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.99670999999999998</v>
@@ -4892,7 +5005,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0.99295999999999995</v>
@@ -4904,7 +5017,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.99390000000000001</v>
@@ -4912,7 +5025,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0.97840000000000005</v>
@@ -4924,7 +5037,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.97887000000000002</v>
@@ -4932,7 +5045,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.98028000000000004</v>
@@ -4968,7 +5081,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>0.95962000000000003</v>
@@ -4980,7 +5093,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0.96103000000000005</v>
@@ -4988,7 +5101,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.96736999999999995</v>
@@ -5024,7 +5137,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.64788999999999997</v>
@@ -5036,7 +5149,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.6169</v>
@@ -5044,7 +5157,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.62770000000000004</v>
@@ -5052,7 +5165,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>0.55586999999999998</v>
@@ -5088,7 +5201,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.99390000000000001</v>
@@ -5100,7 +5213,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>0.99436999999999998</v>
@@ -5112,7 +5225,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>0.99202000000000001</v>
@@ -5130,10 +5243,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5174,7 +5287,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.55745</v>
@@ -5186,7 +5299,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.56489999999999996</v>
@@ -5194,7 +5307,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0.56618000000000002</v>
@@ -5202,7 +5315,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.47383999999999998</v>
@@ -5214,7 +5327,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.46977000000000002</v>
@@ -5222,7 +5335,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.44077</v>
@@ -5230,7 +5343,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.50119000000000002</v>
@@ -5242,7 +5355,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.41348000000000001</v>
@@ -5250,7 +5363,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.48381000000000002</v>
@@ -5262,7 +5375,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.49658000000000002</v>
@@ -5306,7 +5419,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.51495000000000002</v>
@@ -5318,7 +5431,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0.51861999999999997</v>
@@ -5326,7 +5439,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0.51910000000000001</v>
@@ -5334,7 +5447,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0.51822000000000001</v>
@@ -5362,7 +5475,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.45831</v>
@@ -5374,7 +5487,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>0.41425000000000001</v>
@@ -5382,7 +5495,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>0.47589999999999999</v>
@@ -5390,7 +5503,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>0.47666999999999998</v>
@@ -5434,7 +5547,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>0.47381000000000001</v>
@@ -5446,7 +5559,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>0.47099000000000002</v>
@@ -5454,7 +5567,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.44855</v>
@@ -5462,7 +5575,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>0.48259000000000002</v>
@@ -5474,7 +5587,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>0.49945000000000001</v>
@@ -5492,10 +5605,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5520,7 +5633,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0.51951999999999998</v>
@@ -5532,7 +5645,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0.53190999999999999</v>
@@ -5540,7 +5653,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.52966000000000002</v>
@@ -5548,7 +5661,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.52924000000000004</v>
@@ -5556,7 +5669,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0.52049999999999996</v>
@@ -5568,7 +5681,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.52542999999999995</v>
@@ -5576,7 +5689,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.52431000000000005</v>
@@ -5584,7 +5697,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.50183</v>
@@ -5596,7 +5709,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.46189000000000002</v>
@@ -5604,7 +5717,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.49682999999999999</v>
@@ -5612,7 +5725,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.50183</v>
@@ -5624,7 +5737,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.47619</v>
@@ -5632,7 +5745,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.49084</v>
@@ -5660,7 +5773,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0.50726000000000004</v>
@@ -5672,7 +5785,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0.48048000000000002</v>
@@ -5708,7 +5821,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>0.51853000000000005</v>
@@ -5720,7 +5833,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>0.51726000000000005</v>
@@ -5728,7 +5841,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0.49556</v>
@@ -5764,7 +5877,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>0.48837999999999998</v>
@@ -5776,7 +5889,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>0.47089999999999999</v>
@@ -5784,7 +5897,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0.49569999999999997</v>
@@ -5792,7 +5905,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>0.54615000000000002</v>
@@ -5804,7 +5917,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34">
         <v>0.55318999999999996</v>
@@ -5812,7 +5925,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35">
         <v>0.55686000000000002</v>
@@ -5830,10 +5943,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5874,7 +5987,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0.66056000000000004</v>
@@ -5886,7 +5999,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0.66861000000000004</v>
@@ -5894,7 +6007,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0.66883000000000004</v>
@@ -5902,7 +6015,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0.62133000000000005</v>
@@ -5914,7 +6027,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0.65583000000000002</v>
@@ -5922,7 +6035,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0.54978000000000005</v>
@@ -5934,7 +6047,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.56760999999999995</v>
@@ -5942,7 +6055,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.56933</v>
@@ -5950,7 +6063,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.48764000000000002</v>
@@ -5962,7 +6075,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0.54483000000000004</v>
@@ -5970,7 +6083,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0.54805999999999999</v>
@@ -5978,7 +6091,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>0.56138999999999994</v>
@@ -6014,7 +6127,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0.58743999999999996</v>
@@ -6026,7 +6139,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>0.60592000000000001</v>
@@ -6034,7 +6147,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>0.60472000000000004</v>
@@ -6042,7 +6155,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>0.59699999999999998</v>
@@ -6078,7 +6191,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>0.52010999999999996</v>
@@ -6090,7 +6203,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>0.54117000000000004</v>
@@ -6098,7 +6211,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>0.55393999999999999</v>
@@ -6106,7 +6219,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.55693999999999999</v>
@@ -6150,7 +6263,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>0.54471999999999998</v>
@@ -6162,7 +6275,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>0.55967</v>
@@ -6170,7 +6283,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>0.54881000000000002</v>
@@ -6178,7 +6291,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>0.55528</v>
@@ -6186,7 +6299,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>0.70977999999999997</v>
@@ -6198,7 +6311,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>0.71150000000000002</v>
@@ -6206,7 +6319,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42">
         <v>0.71011000000000002</v>
@@ -6214,7 +6327,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43">
         <v>0.71682999999999997</v>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4EBCA5-33E2-4615-B118-0418F7137231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF16760-DC2F-4209-AE1F-DCD2E7268A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="39">
   <si>
     <t>Arrhy</t>
   </si>
@@ -209,6 +209,9 @@
   <si>
     <t>Gamma ROC AUC</t>
   </si>
+  <si>
+    <t>Hepatitis</t>
+  </si>
 </sst>
 </file>
 
@@ -283,10 +286,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2882,24 +2885,24 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="6"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3326,7 +3329,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2">
         <v>0.78588000000000002</v>
@@ -3533,7 +3536,7 @@
       </c>
       <c r="M18" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,A3:A13)</f>
-        <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hep','Pima','PenDigits</v>
+        <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hepatitis','Pima','PenDigits</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
@@ -3571,7 +3574,7 @@
         <f t="shared" si="1"/>
         <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="6">
         <f>N8-K8</f>
         <v>-5.1357367901931017E-2</v>
       </c>
@@ -3716,7 +3719,7 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:N32 B46:N1048576 C33:N45">
+  <conditionalFormatting sqref="B1:N32 C33:N45 B46:N1048576">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>B1=MAX($B1:$N1)</formula>
     </cfRule>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF16760-DC2F-4209-AE1F-DCD2E7268A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84559137-CA40-480F-8C68-1A1A97D009DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="41">
   <si>
     <t>Arrhy</t>
   </si>
@@ -207,10 +207,16 @@
     <t>Skewness</t>
   </si>
   <si>
-    <t>Gamma ROC AUC</t>
+    <t>Hepatitis</t>
   </si>
   <si>
-    <t>Hepatitis</t>
+    <t>Gamma MAX</t>
+  </si>
+  <si>
+    <t>Gamma MedMax</t>
+  </si>
+  <si>
+    <t>Gamma MedMax Q-Q Plot</t>
   </si>
 </sst>
 </file>
@@ -279,7 +285,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -290,6 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2874,16 +2881,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" customWidth="1"/>
+    <col min="16" max="16" width="15.85546875" customWidth="1"/>
+    <col min="17" max="17" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="7" t="s">
         <v>33</v>
@@ -2904,7 +2913,7 @@
       </c>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -2945,13 +2954,19 @@
         <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -2998,7 +3013,7 @@
         <v>0.97450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3045,7 +3060,7 @@
         <v>0.85409999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3092,7 +3107,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3139,7 +3154,7 @@
         <v>0.98670000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3186,7 +3201,7 @@
         <v>0.92220000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3233,7 +3248,7 @@
         <v>0.98599999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3280,7 +3295,7 @@
         <v>0.99390000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3327,9 +3342,9 @@
         <v>0.93869999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2">
         <v>0.78588000000000002</v>
@@ -3374,7 +3389,7 @@
         <v>0.93610000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3421,7 +3436,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3468,7 +3483,7 @@
         <v>0.97860000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3574,10 +3589,7 @@
         <f t="shared" si="1"/>
         <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
       </c>
-      <c r="N24" s="6">
-        <f>N8-K8</f>
-        <v>-5.1357367901931017E-2</v>
-      </c>
+      <c r="N24" s="6"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
@@ -3606,7 +3618,7 @@
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
-        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma ROC AUC</v>
+        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma MAX</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -3719,7 +3731,7 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:N32 C33:N45 B46:N1048576">
+  <conditionalFormatting sqref="B1:N32 C33:N45 B46:N1048576 P2:Q2">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>B1=MAX($B1:$N1)</formula>
     </cfRule>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84559137-CA40-480F-8C68-1A1A97D009DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16E62DE-9CA9-4038-8B93-CF0327C85AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="40">
   <si>
     <t>Arrhy</t>
   </si>
@@ -210,13 +210,10 @@
     <t>Hepatitis</t>
   </si>
   <si>
-    <t>Gamma MAX</t>
+    <t>Gamma MedMax Q-Q Plot</t>
   </si>
   <si>
-    <t>Gamma MedMax</t>
-  </si>
-  <si>
-    <t>Gamma MedMax Q-Q Plot</t>
+    <t>Log Gamma</t>
   </si>
 </sst>
 </file>
@@ -285,7 +282,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -296,7 +293,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2881,18 +2877,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="16.5703125" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" customWidth="1"/>
     <col min="16" max="16" width="15.85546875" customWidth="1"/>
     <col min="17" max="17" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="7" t="s">
         <v>33</v>
@@ -2913,7 +2910,7 @@
       </c>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -2954,19 +2951,21 @@
         <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3012,8 +3011,14 @@
       <c r="O3" s="2">
         <v>0.97450000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P3" s="3">
+        <v>0.76087259271048802</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.99539999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3059,8 +3064,14 @@
       <c r="O4" s="2">
         <v>0.85409999999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P4" s="3">
+        <v>0.74000850340136004</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3106,8 +3117,14 @@
       <c r="O5" s="2">
         <v>0.72499999999999998</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P5" s="3">
+        <v>0.84565384615384598</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.99239999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3153,8 +3170,14 @@
       <c r="O6" s="2">
         <v>0.98670000000000002</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P6" s="3">
+        <v>0.99366197183098603</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.9395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3200,8 +3223,14 @@
       <c r="O7" s="2">
         <v>0.92220000000000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P7" s="3">
+        <v>0.65056312716279296</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.72509999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3247,8 +3276,14 @@
       <c r="O8" s="2">
         <v>0.98599999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P8" s="3">
+        <v>0.53219670283218201</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.99229999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3294,8 +3329,14 @@
       <c r="O9" s="2">
         <v>0.99390000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P9" s="3">
+        <v>0.69902777777777703</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.99390000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3341,8 +3382,14 @@
       <c r="O10" s="2">
         <v>0.93869999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P10" s="3">
+        <v>0.87777777777777699</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.97550000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -3388,8 +3435,14 @@
       <c r="O11" s="2">
         <v>0.93610000000000004</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P11" s="3">
+        <v>0.78587830080367405</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3435,8 +3488,14 @@
       <c r="O12" s="2">
         <v>0.997</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P12" s="3">
+        <v>0.73567164179104405</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.99080000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3482,8 +3541,14 @@
       <c r="O13" s="2">
         <v>0.97860000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P13" s="3">
+        <v>0.98741368805848895</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.99809999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3543,6 +3608,8 @@
         <f>AVERAGE(O3:O13)</f>
         <v>0.93570909090909093</v>
       </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
@@ -3618,7 +3685,7 @@
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
-        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma MAX</v>
+        <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -3731,7 +3798,7 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:N32 C33:N45 B46:N1048576 P2:Q2">
+  <conditionalFormatting sqref="B1:N32 P2:Q2 C33:N45 B46:N1048576">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>B1=MAX($B1:$N1)</formula>
     </cfRule>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16E62DE-9CA9-4038-8B93-CF0327C85AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6324BFBE-04E5-4573-8131-89DDF8E27574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="41">
   <si>
     <t>Arrhy</t>
   </si>
@@ -210,10 +210,13 @@
     <t>Hepatitis</t>
   </si>
   <si>
-    <t>Gamma MedMax Q-Q Plot</t>
+    <t>Log Gamma</t>
   </si>
   <si>
-    <t>Log Gamma</t>
+    <t>LogNorm</t>
+  </si>
+  <si>
+    <t>BoxPlot</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -293,13 +296,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2877,7 +2905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -2889,7 +2917,7 @@
     <col min="17" max="17" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="7" t="s">
         <v>33</v>
@@ -2910,7 +2938,7 @@
       </c>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:19" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -2957,15 +2985,18 @@
         <v>32</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="4"/>
       <c r="S2" s="4"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3014,11 +3045,15 @@
       <c r="P3" s="3">
         <v>0.76087259271048802</v>
       </c>
-      <c r="Q3" s="3">
-        <v>0.99539999999999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3">
+        <v>0.75987784497851296</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0.75567006207225795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3067,11 +3102,15 @@
       <c r="P4" s="3">
         <v>0.74000850340136004</v>
       </c>
-      <c r="Q4" s="3">
-        <v>0.96550000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3">
+        <v>0.73915816326530603</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.63116496598639404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3120,11 +3159,15 @@
       <c r="P5" s="3">
         <v>0.84565384615384598</v>
       </c>
-      <c r="Q5" s="3">
-        <v>0.99239999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3">
+        <v>0.84565384615384598</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0.81988461538461499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3173,11 +3216,15 @@
       <c r="P6" s="3">
         <v>0.99366197183098603</v>
       </c>
-      <c r="Q6" s="3">
-        <v>0.9395</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3">
+        <v>0.99624413145539903</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0.92957746478873204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3226,11 +3273,15 @@
       <c r="P7" s="3">
         <v>0.65056312716279296</v>
       </c>
-      <c r="Q7" s="3">
-        <v>0.72509999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3">
+        <v>0.65016626175164505</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0.58773988623427098</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3279,11 +3330,15 @@
       <c r="P8" s="3">
         <v>0.53219670283218201</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0.99229999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3">
+        <v>0.53170353670564996</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.52973087219951998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3332,11 +3387,15 @@
       <c r="P9" s="3">
         <v>0.69902777777777703</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0.99390000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3">
+        <v>0.70052777777777697</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0.65786111111111101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3385,11 +3444,15 @@
       <c r="P10" s="3">
         <v>0.87777777777777699</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0.97550000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3">
+        <v>0.87615176151761498</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0.862059620596206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -3438,11 +3501,15 @@
       <c r="P11" s="3">
         <v>0.78587830080367405</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0.96550000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3">
+        <v>0.78817451205510902</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0.78415614236509701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3491,11 +3558,15 @@
       <c r="P12" s="3">
         <v>0.73567164179104405</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0.99080000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3">
+        <v>0.73719029850746198</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0.73098880597014904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3544,11 +3615,15 @@
       <c r="P13" s="3">
         <v>0.98741368805848895</v>
       </c>
-      <c r="Q13" s="3">
-        <v>0.99809999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3">
+        <v>0.98738830219333795</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.96613779447603498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3608,8 +3683,19 @@
         <f>AVERAGE(O3:O13)</f>
         <v>0.93570909090909093</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <f>AVERAGE(P3:P13)</f>
+        <v>0.78261144820912876</v>
+      </c>
       <c r="Q14" s="3"/>
+      <c r="R14" s="3">
+        <f>AVERAGE(R3:R13)</f>
+        <v>0.78293058512378733</v>
+      </c>
+      <c r="T14" s="3">
+        <f>AVERAGE(T3:T13)</f>
+        <v>0.75045194010767158</v>
+      </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
@@ -3798,13 +3884,13 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:N32 P2:Q2 C33:N45 B46:N1048576">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>B1=MAX($B1:$N1)</formula>
+  <conditionalFormatting sqref="B3:N14 P3:P14 R3:R14 T3:T14">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\Documents\GitHub\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6324BFBE-04E5-4573-8131-89DDF8E27574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DBCB9-04DB-4355-885C-89C865A11373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="43">
   <si>
     <t>Arrhy</t>
   </si>
@@ -218,6 +218,12 @@
   <si>
     <t>BoxPlot</t>
   </si>
+  <si>
+    <t>Log Gamma R^2</t>
+  </si>
+  <si>
+    <t>Log Norm R^2</t>
+  </si>
 </sst>
 </file>
 
@@ -285,7 +291,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -296,38 +302,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -617,19 +598,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.1328125" customWidth="1"/>
+    <col min="2" max="2" width="13.86328125" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" customWidth="1"/>
+    <col min="12" max="12" width="10.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -679,7 +660,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -729,7 +710,7 @@
         <v>0.73385</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -779,7 +760,7 @@
         <v>0.64966000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -829,7 +810,7 @@
         <v>0.63968999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -879,7 +860,7 @@
         <v>0.99436999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -929,7 +910,7 @@
         <v>0.49945000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -979,7 +960,7 @@
         <v>0.55686000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1029,7 +1010,7 @@
         <v>0.71682999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1079,7 +1060,7 @@
         <v>0.89539000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1110,7 @@
         <v>0.82721</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1179,7 +1160,7 @@
         <v>0.70121</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1229,7 +1210,7 @@
         <v>0.96694999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1294,17 +1275,17 @@
         <v>0.74376999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1312,7 +1293,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -1320,7 +1301,7 @@
         <v>2.0370831182289302</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1328,7 +1309,7 @@
         <v>3.1547216312678601</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1336,7 +1317,7 @@
         <v>9.8845764865245496</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1325,7 @@
         <v>3.5183738979013799</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1352,7 +1333,7 @@
         <v>3.2411972220237102</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1360,7 +1341,7 @@
         <v>1.8064453738353601</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1368,7 +1349,7 @@
         <v>0.81389733258028796</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1376,7 +1357,7 @@
         <v>2.7273997511512502</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1365,7 @@
         <v>0.39759268151465099</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1392,7 +1373,7 @@
         <v>1.26708352406697</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1400,7 +1381,7 @@
         <v>1.95101294625013</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1418,9 +1399,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F9DFA3-0E78-460F-9480-3FC988D2C4F5}">
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1428,7 +1409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1440,7 +1421,7 @@
         <v>0.87480000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1448,7 +1429,7 @@
         <v>0.86938000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1456,7 +1437,7 @@
         <v>0.87480000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1468,7 +1449,7 @@
         <v>0.88319999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1476,7 +1457,7 @@
         <v>0.86775000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1488,7 +1469,7 @@
         <v>0.86667000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1496,7 +1477,7 @@
         <v>0.58808000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1504,7 +1485,7 @@
         <v>0.86667000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1516,7 +1497,7 @@
         <v>0.86504000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1524,7 +1505,7 @@
         <v>0.86504000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1536,7 +1517,7 @@
         <v>0.83957000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1544,7 +1525,7 @@
         <v>0.61761999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1552,7 +1533,7 @@
         <v>0.83957000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1564,7 +1545,7 @@
         <v>0.77886</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1572,7 +1553,7 @@
         <v>0.73333000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1580,7 +1561,7 @@
         <v>0.77886</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1592,7 +1573,7 @@
         <v>0.72926999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1600,7 +1581,7 @@
         <v>0.55501</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1608,7 +1589,7 @@
         <v>0.72926999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1616,7 +1597,7 @@
         <v>0.71220000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1628,7 +1609,7 @@
         <v>0.85799000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -1636,7 +1617,7 @@
         <v>0.84714999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1644,7 +1625,7 @@
         <v>0.85799000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1656,7 +1637,7 @@
         <v>0.74200999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1664,7 +1645,7 @@
         <v>0.71762000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1672,7 +1653,7 @@
         <v>0.74200999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1684,7 +1665,7 @@
         <v>0.90351999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +1673,7 @@
         <v>0.60487999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1700,7 +1681,7 @@
         <v>0.62385000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1708,7 +1689,7 @@
         <v>0.90351999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1720,7 +1701,7 @@
         <v>0.80379</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1728,7 +1709,7 @@
         <v>0.74958999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -1736,7 +1717,7 @@
         <v>0.80379</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -1748,7 +1729,7 @@
         <v>0.89539000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -1756,7 +1737,7 @@
         <v>0.87858999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -1772,9 +1753,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEBCE60-A305-4996-8394-EDFED30DAA67}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1782,7 +1763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1794,7 +1775,7 @@
         <v>0.78588000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1802,7 +1783,7 @@
         <v>0.77842</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1810,7 +1791,7 @@
         <v>0.77612000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1822,7 +1803,7 @@
         <v>0.74856</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1830,7 +1811,7 @@
         <v>0.74856</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1838,7 +1819,7 @@
         <v>0.74168000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1850,7 +1831,7 @@
         <v>0.80367</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1858,7 +1839,7 @@
         <v>0.80023</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1866,7 +1847,7 @@
         <v>0.80367</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1878,7 +1859,7 @@
         <v>0.73823000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1886,7 +1867,7 @@
         <v>0.73363999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1894,7 +1875,7 @@
         <v>0.73823000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1902,7 +1883,7 @@
         <v>0.73823000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1914,7 +1895,7 @@
         <v>0.72331000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1922,7 +1903,7 @@
         <v>0.72331000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1930,7 +1911,7 @@
         <v>0.70665999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1938,7 +1919,7 @@
         <v>0.72272999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1950,7 +1931,7 @@
         <v>0.73823000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1958,7 +1939,7 @@
         <v>0.71641999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1966,7 +1947,7 @@
         <v>0.73823000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1978,7 +1959,7 @@
         <v>0.74970999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1986,7 +1967,7 @@
         <v>0.74339999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1994,7 +1975,7 @@
         <v>0.74455000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2002,7 +1983,7 @@
         <v>0.74970999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -2014,7 +1995,7 @@
         <v>0.70952999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2022,7 +2003,7 @@
         <v>0.70952999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2030,7 +2011,7 @@
         <v>0.70838000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2042,7 +2023,7 @@
         <v>0.71182999999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2050,7 +2031,7 @@
         <v>0.70608000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -2058,7 +2039,7 @@
         <v>0.71182999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -2070,7 +2051,7 @@
         <v>0.82892999999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -2078,7 +2059,7 @@
         <v>0.78415999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -2086,7 +2067,7 @@
         <v>0.82892999999999994</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -2094,7 +2075,7 @@
         <v>0.78874999999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -2106,7 +2087,7 @@
         <v>0.60275999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -2114,7 +2095,7 @@
         <v>0.53156999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -2122,7 +2103,7 @@
         <v>0.60275999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -2134,7 +2115,7 @@
         <v>0.82721</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -2142,7 +2123,7 @@
         <v>0.79564000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -2150,7 +2131,7 @@
         <v>0.82203999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -2166,9 +2147,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8693EBA-F9E5-4205-8DE2-5CF3643D9239}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2176,7 +2157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2188,7 +2169,7 @@
         <v>0.73224</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2196,7 +2177,7 @@
         <v>0.73224</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2204,7 +2185,7 @@
         <v>0.73192999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2212,7 +2193,7 @@
         <v>0.73187000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2224,7 +2205,7 @@
         <v>0.72943999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2232,7 +2213,7 @@
         <v>0.71386000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2240,7 +2221,7 @@
         <v>0.72921000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -2248,7 +2229,7 @@
         <v>0.72943999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2260,7 +2241,7 @@
         <v>0.68955</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -2268,7 +2249,7 @@
         <v>0.68955</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2280,7 +2261,7 @@
         <v>0.62131000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2288,7 +2269,7 @@
         <v>0.62131000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2281,7 @@
         <v>0.60921999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2308,7 +2289,7 @@
         <v>0.60921999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2320,7 +2301,7 @@
         <v>0.57003999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2328,7 +2309,7 @@
         <v>0.56925000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -2336,7 +2317,7 @@
         <v>0.56938</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -2344,7 +2325,7 @@
         <v>0.57003999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -2356,7 +2337,7 @@
         <v>0.63636999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -2368,7 +2349,7 @@
         <v>0.76080999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2376,7 +2357,7 @@
         <v>0.75512999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -2384,7 +2365,7 @@
         <v>0.76080999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2396,7 +2377,7 @@
         <v>0.55620999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2404,7 +2385,7 @@
         <v>0.53607000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -2416,7 +2397,7 @@
         <v>0.72887999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -2424,7 +2405,7 @@
         <v>0.72567999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -2432,7 +2413,7 @@
         <v>0.72887999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2444,7 +2425,7 @@
         <v>0.61728000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2452,7 +2433,7 @@
         <v>0.61375000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2460,7 +2441,7 @@
         <v>0.61621999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -2472,7 +2453,7 @@
         <v>0.70121</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -2480,7 +2461,7 @@
         <v>0.69167999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2496,9 +2477,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5377EC-BA22-47EB-98DB-A8ABB998676D}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2506,7 +2487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2518,7 +2499,7 @@
         <v>0.99212</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2526,7 +2507,7 @@
         <v>0.99212</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2534,7 +2515,7 @@
         <v>0.99175999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2546,7 +2527,7 @@
         <v>0.99160000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2554,7 +2535,7 @@
         <v>0.99160000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2562,7 +2543,7 @@
         <v>0.99158000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2570,7 +2551,7 @@
         <v>0.99150000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -2582,7 +2563,7 @@
         <v>0.96580999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2590,7 +2571,7 @@
         <v>0.59387999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -2598,7 +2579,7 @@
         <v>0.96469000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2606,7 +2587,7 @@
         <v>0.96580999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2618,7 +2599,7 @@
         <v>0.96679999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2626,7 +2607,7 @@
         <v>0.96197999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2634,7 +2615,7 @@
         <v>0.96679999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2627,7 @@
         <v>0.96231</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2654,7 +2635,7 @@
         <v>0.55501</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2662,7 +2643,7 @@
         <v>0.96167000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2670,7 +2651,7 @@
         <v>0.96231</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -2682,7 +2663,7 @@
         <v>0.75034000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -2690,7 +2671,7 @@
         <v>0.58501000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2698,7 +2679,7 @@
         <v>0.48826999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -2706,7 +2687,7 @@
         <v>0.75034000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2718,7 +2699,7 @@
         <v>0.96431999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2726,7 +2707,7 @@
         <v>0.96277999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2734,7 +2715,7 @@
         <v>0.96431999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2746,7 +2727,7 @@
         <v>0.97979000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2754,7 +2735,7 @@
         <v>0.95459000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -2762,7 +2743,7 @@
         <v>0.97979000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2774,7 +2755,7 @@
         <v>0.82213999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -2782,7 +2763,7 @@
         <v>0.64922000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2790,7 +2771,7 @@
         <v>0.67037999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -2798,7 +2779,7 @@
         <v>0.82213999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -2810,7 +2791,7 @@
         <v>0.97790999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -2818,7 +2799,7 @@
         <v>0.96238999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -2826,7 +2807,7 @@
         <v>0.97790999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -2838,7 +2819,7 @@
         <v>0.95711999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -2846,7 +2827,7 @@
         <v>0.57008999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -2854,7 +2835,7 @@
         <v>0.95633000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -2862,7 +2843,7 @@
         <v>0.95711999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -2874,7 +2855,7 @@
         <v>0.96694999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -2882,7 +2863,7 @@
         <v>0.94615000000000005</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -2890,7 +2871,7 @@
         <v>0.94364999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -2906,18 +2887,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC67C2C-7E75-4C4C-A5D6-03334A2710BD}">
   <dimension ref="A1:T45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="13" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" customWidth="1"/>
-    <col min="17" max="17" width="24.140625" customWidth="1"/>
+    <col min="3" max="13" width="9.1328125" customWidth="1"/>
+    <col min="14" max="14" width="16.59765625" customWidth="1"/>
+    <col min="15" max="15" width="18.265625" customWidth="1"/>
+    <col min="16" max="16" width="15.86328125" customWidth="1"/>
+    <col min="17" max="17" width="24.1328125" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
       <c r="B1" s="7" t="s">
         <v>33</v>
@@ -2938,7 +2920,7 @@
       </c>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -2987,16 +2969,20 @@
       <c r="P2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="4"/>
+      <c r="Q2" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="R2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="8" t="s">
+      <c r="S2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3045,15 +3031,20 @@
       <c r="P3" s="3">
         <v>0.76087259271048802</v>
       </c>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="3">
+        <v>0.99539999999999995</v>
+      </c>
       <c r="R3" s="3">
         <v>0.75987784497851296</v>
       </c>
+      <c r="S3" s="3">
+        <v>0.99490000000000001</v>
+      </c>
       <c r="T3" s="3">
         <v>0.75567006207225795</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3102,15 +3093,20 @@
       <c r="P4" s="3">
         <v>0.74000850340136004</v>
       </c>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="3">
+        <v>0.96550000000000002</v>
+      </c>
       <c r="R4" s="3">
         <v>0.73915816326530603</v>
       </c>
+      <c r="S4" s="3">
+        <v>0.96919999999999995</v>
+      </c>
       <c r="T4" s="3">
         <v>0.63116496598639404</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3159,15 +3155,20 @@
       <c r="P5" s="3">
         <v>0.84565384615384598</v>
       </c>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="3">
+        <v>0.99239999999999995</v>
+      </c>
       <c r="R5" s="3">
         <v>0.84565384615384598</v>
       </c>
+      <c r="S5" s="3">
+        <v>0.99250000000000005</v>
+      </c>
       <c r="T5" s="3">
         <v>0.81988461538461499</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3216,15 +3217,20 @@
       <c r="P6" s="3">
         <v>0.99366197183098603</v>
       </c>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="3">
+        <v>0.9395</v>
+      </c>
       <c r="R6" s="3">
         <v>0.99624413145539903</v>
       </c>
+      <c r="S6" s="3">
+        <v>0.93279999999999996</v>
+      </c>
       <c r="T6" s="3">
         <v>0.92957746478873204</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3273,15 +3279,20 @@
       <c r="P7" s="3">
         <v>0.65056312716279296</v>
       </c>
-      <c r="Q7" s="3"/>
+      <c r="Q7" s="3">
+        <v>0.72509999999999997</v>
+      </c>
       <c r="R7" s="3">
         <v>0.65016626175164505</v>
       </c>
+      <c r="S7" s="3">
+        <v>0.83940000000000003</v>
+      </c>
       <c r="T7" s="3">
         <v>0.58773988623427098</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3330,15 +3341,20 @@
       <c r="P8" s="3">
         <v>0.53219670283218201</v>
       </c>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="3">
+        <v>0.99229999999999996</v>
+      </c>
       <c r="R8" s="3">
         <v>0.53170353670564996</v>
       </c>
+      <c r="S8" s="3">
+        <v>0.98950000000000005</v>
+      </c>
       <c r="T8" s="3">
         <v>0.52973087219951998</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3387,15 +3403,20 @@
       <c r="P9" s="3">
         <v>0.69902777777777703</v>
       </c>
-      <c r="Q9" s="3"/>
+      <c r="Q9" s="3">
+        <v>0.99390000000000001</v>
+      </c>
       <c r="R9" s="3">
         <v>0.70052777777777697</v>
       </c>
+      <c r="S9" s="3">
+        <v>0.99309999999999998</v>
+      </c>
       <c r="T9" s="3">
         <v>0.65786111111111101</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3444,15 +3465,20 @@
       <c r="P10" s="3">
         <v>0.87777777777777699</v>
       </c>
-      <c r="Q10" s="3"/>
+      <c r="Q10" s="3">
+        <v>0.97550000000000003</v>
+      </c>
       <c r="R10" s="3">
         <v>0.87615176151761498</v>
       </c>
+      <c r="S10" s="3">
+        <v>0.98719999999999997</v>
+      </c>
       <c r="T10" s="3">
         <v>0.862059620596206</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -3501,15 +3527,20 @@
       <c r="P11" s="3">
         <v>0.78587830080367405</v>
       </c>
-      <c r="Q11" s="3"/>
+      <c r="Q11" s="3">
+        <v>0.96550000000000002</v>
+      </c>
       <c r="R11" s="3">
         <v>0.78817451205510902</v>
       </c>
+      <c r="S11" s="3">
+        <v>0.96450000000000002</v>
+      </c>
       <c r="T11" s="3">
         <v>0.78415614236509701</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3558,15 +3589,20 @@
       <c r="P12" s="3">
         <v>0.73567164179104405</v>
       </c>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="3">
+        <v>0.99080000000000001</v>
+      </c>
       <c r="R12" s="3">
         <v>0.73719029850746198</v>
       </c>
+      <c r="S12" s="3">
+        <v>0.99060000000000004</v>
+      </c>
       <c r="T12" s="3">
         <v>0.73098880597014904</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3615,15 +3651,20 @@
       <c r="P13" s="3">
         <v>0.98741368805848895</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="3">
+        <v>0.99809999999999999</v>
+      </c>
       <c r="R13" s="3">
         <v>0.98738830219333795</v>
       </c>
+      <c r="S13" s="3">
+        <v>0.99860000000000004</v>
+      </c>
       <c r="T13" s="3">
         <v>0.96613779447603498</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3687,17 +3728,24 @@
         <f>AVERAGE(P3:P13)</f>
         <v>0.78261144820912876</v>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="3">
+        <f>AVERAGE(Q3:Q13)</f>
+        <v>0.95763636363636384</v>
+      </c>
       <c r="R14" s="3">
         <f>AVERAGE(R3:R13)</f>
         <v>0.78293058512378733</v>
       </c>
+      <c r="S14" s="3">
+        <f>AVERAGE(S3:S13)</f>
+        <v>0.96839090909090897</v>
+      </c>
       <c r="T14" s="3">
         <f>AVERAGE(T3:T13)</f>
         <v>0.75045194010767158</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B18" t="str">
         <f>_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B3:N3),"]")</f>
         <v>[0.752,0.75008,0.74421,0.74339,0.74111,0.73452,0.72669,0.74176,0.66101,0.72286,0.73154,0.73385,0.761081489734203]</v>
@@ -3707,74 +3755,74 @@
         <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hepatitis','Pima','PenDigits</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" t="str">
         <f t="shared" ref="B19:B28" si="1">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
         <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242]</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846]</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774]</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444]</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069]</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B24" t="str">
         <f t="shared" si="1"/>
         <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
       </c>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B25" t="str">
         <f t="shared" si="1"/>
         <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048]</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956]</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477]</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025]</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B31" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
         <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -3782,7 +3830,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -3790,7 +3838,7 @@
         <v>0.97450000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -3798,7 +3846,7 @@
         <v>0.85409999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>2</v>
       </c>
@@ -3806,7 +3854,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -3814,7 +3862,7 @@
         <v>0.98670000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -3822,7 +3870,7 @@
         <v>0.92220000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3830,7 +3878,7 @@
         <v>0.98599999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -3838,7 +3886,7 @@
         <v>0.99390000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -3846,7 +3894,7 @@
         <v>0.93869999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -3854,7 +3902,7 @@
         <v>0.93610000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3862,7 +3910,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -3870,7 +3918,7 @@
         <v>0.97860000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -3884,13 +3932,13 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:N14 P3:P14 R3:R14 T3:T14">
-    <cfRule type="expression" dxfId="2" priority="2">
+  <conditionalFormatting sqref="B3:N14 P3:P14 R3:R14 T3:T14 S3:S13">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3902,9 +3950,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814B012A-D937-47C4-8AC9-6A6E5FDF72BE}">
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3912,7 +3960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3920,7 +3968,7 @@
         <v>0.74761</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3928,7 +3976,7 @@
         <v>0.75158000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3940,7 +3988,7 @@
         <v>0.75205</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3948,7 +3996,7 @@
         <v>0.74997999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3956,7 +4004,7 @@
         <v>0.74456999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3964,7 +4012,7 @@
         <v>0.74836999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3976,7 +4024,7 @@
         <v>0.75007999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3984,7 +4032,7 @@
         <v>0.75007999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3992,7 +4040,7 @@
         <v>0.71584000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -4000,7 +4048,7 @@
         <v>0.72428000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4012,7 +4060,7 @@
         <v>0.74421000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4020,7 +4068,7 @@
         <v>0.74414999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -4028,7 +4076,7 @@
         <v>0.71930000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -4036,7 +4084,7 @@
         <v>0.73812</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -4048,7 +4096,7 @@
         <v>0.74339</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4056,7 +4104,7 @@
         <v>0.74319999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4064,7 +4112,7 @@
         <v>0.71847000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -4072,7 +4120,7 @@
         <v>0.73836000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -4084,7 +4132,7 @@
         <v>0.74111000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4092,7 +4140,7 @@
         <v>0.74097000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -4100,7 +4148,7 @@
         <v>0.71986000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -4112,7 +4160,7 @@
         <v>0.73451999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -4120,7 +4168,7 @@
         <v>0.73451999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -4132,7 +4180,7 @@
         <v>0.72668999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -4140,7 +4188,7 @@
         <v>0.72275999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4148,7 +4196,7 @@
         <v>0.72668999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -4160,7 +4208,7 @@
         <v>0.74175999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -4168,7 +4216,7 @@
         <v>0.74175999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4180,7 +4228,7 @@
         <v>0.66100999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4188,7 +4236,7 @@
         <v>0.66100999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -4196,7 +4244,7 @@
         <v>0.71103000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -4208,7 +4256,7 @@
         <v>0.72285999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -4216,7 +4264,7 @@
         <v>0.72285999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -4224,7 +4272,7 @@
         <v>0.70821999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -4236,7 +4284,7 @@
         <v>0.73153999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -4244,7 +4292,7 @@
         <v>0.73038000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -4252,7 +4300,7 @@
         <v>0.73153999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -4264,7 +4312,7 @@
         <v>0.73385</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -4272,7 +4320,7 @@
         <v>0.72340000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -4280,7 +4328,7 @@
         <v>0.73385</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -4297,9 +4345,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96173FC3-F951-424B-A654-7BA719E64DFA}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4307,7 +4355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4315,7 +4363,7 @@
         <v>0.64753000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4327,7 +4375,7 @@
         <v>0.65234999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4335,7 +4383,7 @@
         <v>0.63349999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -4343,7 +4391,7 @@
         <v>0.64115999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -4355,7 +4403,7 @@
         <v>0.64398999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -4367,7 +4415,7 @@
         <v>0.61195999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4375,7 +4423,7 @@
         <v>0.61195999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -4383,7 +4431,7 @@
         <v>0.60189999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -4391,7 +4439,7 @@
         <v>0.46357999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -4403,7 +4451,7 @@
         <v>0.60728000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -4411,7 +4459,7 @@
         <v>0.60643000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4419,7 +4467,7 @@
         <v>0.60728000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4431,7 +4479,7 @@
         <v>0.58311999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4439,7 +4487,7 @@
         <v>0.56738999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -4447,7 +4495,7 @@
         <v>0.58311999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -4455,7 +4503,7 @@
         <v>0.57865999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4467,7 +4515,7 @@
         <v>0.55315000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4475,7 +4523,7 @@
         <v>0.54052999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -4483,7 +4531,7 @@
         <v>0.55315000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -4495,7 +4543,7 @@
         <v>0.52607999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4503,7 +4551,7 @@
         <v>0.52607999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4511,7 +4559,7 @@
         <v>0.51651000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -4523,7 +4571,7 @@
         <v>0.66993000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -4531,7 +4579,7 @@
         <v>0.66908000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -4539,7 +4587,7 @@
         <v>0.66993000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4547,7 +4595,7 @@
         <v>0.64881</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -4559,7 +4607,7 @@
         <v>0.58672999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4567,7 +4615,7 @@
         <v>0.57808999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4575,7 +4623,7 @@
         <v>0.58672999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4583,7 +4631,7 @@
         <v>0.58574000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -4595,7 +4643,7 @@
         <v>0.60218000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -4603,7 +4651,7 @@
         <v>0.40178999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -4611,7 +4659,7 @@
         <v>0.49008000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4623,7 +4671,7 @@
         <v>0.59197999999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -4631,7 +4679,7 @@
         <v>0.59197999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -4639,7 +4687,7 @@
         <v>0.58248</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -4647,7 +4695,7 @@
         <v>0.58389999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -4659,7 +4707,7 @@
         <v>0.64966000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -4667,7 +4715,7 @@
         <v>0.58687999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -4675,7 +4723,7 @@
         <v>0.64966000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -4691,9 +4739,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFC0E0F-6E6F-42A6-8CF4-86ECBE8FE863}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -4701,7 +4749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4713,7 +4761,7 @@
         <v>0.81762000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4721,7 +4769,7 @@
         <v>0.81762000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4729,7 +4777,7 @@
         <v>0.63468999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -4741,7 +4789,7 @@
         <v>0.72785</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -4749,7 +4797,7 @@
         <v>0.72785</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -4761,7 +4809,7 @@
         <v>0.78208</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4769,7 +4817,7 @@
         <v>0.78208</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -4777,7 +4825,7 @@
         <v>0.72138000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4833,7 @@
         <v>0.72423000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -4797,7 +4845,7 @@
         <v>0.76607999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -4805,7 +4853,7 @@
         <v>0.76276999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4813,7 +4861,7 @@
         <v>0.76607999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4825,7 +4873,7 @@
         <v>0.78991999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4833,7 +4881,7 @@
         <v>0.78991999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -4841,7 +4889,7 @@
         <v>0.76131000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -4849,7 +4897,7 @@
         <v>0.76400000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4861,7 +4909,7 @@
         <v>0.84753999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4869,7 +4917,7 @@
         <v>0.35654000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -4877,7 +4925,7 @@
         <v>0.84462000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4885,7 +4933,7 @@
         <v>0.84753999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4897,7 +4945,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4905,7 +4953,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -4913,7 +4961,7 @@
         <v>0.77712000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -4925,7 +4973,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -4933,7 +4981,7 @@
         <v>0.27792</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4941,7 +4989,7 @@
         <v>0.26430999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -4953,7 +5001,7 @@
         <v>0.69191999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4961,7 +5009,7 @@
         <v>0.62185000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4969,7 +5017,7 @@
         <v>0.65207999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4977,7 +5025,7 @@
         <v>0.66554000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -4989,7 +5037,7 @@
         <v>0.71584999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -4997,7 +5045,7 @@
         <v>0.71584999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -5005,7 +5053,7 @@
         <v>0.67945999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -5013,7 +5061,7 @@
         <v>0.69762000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -5025,7 +5073,7 @@
         <v>0.79884999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -5033,7 +5081,7 @@
         <v>0.79884999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -5041,7 +5089,7 @@
         <v>0.79408000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>29</v>
       </c>
@@ -5053,7 +5101,7 @@
         <v>0.63968999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -5061,7 +5109,7 @@
         <v>0.46515000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -5069,7 +5117,7 @@
         <v>0.38338</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -5085,9 +5133,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF3F352-3EF6-4C40-860C-2F33291BDFA8}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5095,7 +5143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5107,7 +5155,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5115,7 +5163,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -5127,7 +5175,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -5135,7 +5183,7 @@
         <v>0.99436999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5143,7 +5191,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -5155,7 +5203,7 @@
         <v>0.99670999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5163,7 +5211,7 @@
         <v>0.99531000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -5171,7 +5219,7 @@
         <v>0.99670999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -5183,7 +5231,7 @@
         <v>0.99390000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5191,7 +5239,7 @@
         <v>0.99390000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -5203,7 +5251,7 @@
         <v>0.98028000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -5211,7 +5259,7 @@
         <v>0.97887000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -5219,7 +5267,7 @@
         <v>0.98028000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -5231,7 +5279,7 @@
         <v>0.96526000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -5239,7 +5287,7 @@
         <v>0.96338000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -5247,7 +5295,7 @@
         <v>0.96526000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -5259,7 +5307,7 @@
         <v>0.96736999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -5267,7 +5315,7 @@
         <v>0.96103000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -5275,7 +5323,7 @@
         <v>0.96736999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -5287,7 +5335,7 @@
         <v>0.99483999999999995</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -5295,7 +5343,7 @@
         <v>0.99436999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -5303,7 +5351,7 @@
         <v>0.99483999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -5315,7 +5363,7 @@
         <v>0.64788999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -5323,7 +5371,7 @@
         <v>0.6169</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -5331,7 +5379,7 @@
         <v>0.62770000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -5339,7 +5387,7 @@
         <v>0.55586999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -5351,7 +5399,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -5359,7 +5407,7 @@
         <v>0.99624000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -5367,7 +5415,7 @@
         <v>0.99717999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -5379,7 +5427,7 @@
         <v>0.99390000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -5391,7 +5439,7 @@
         <v>0.99436999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -5407,9 +5455,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A4D3B8-EA7D-4BBD-950A-F6390B43B165}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5417,7 +5465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5429,7 +5477,7 @@
         <v>0.57347000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5437,7 +5485,7 @@
         <v>0.56925999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5445,7 +5493,7 @@
         <v>0.57174000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -5453,7 +5501,7 @@
         <v>0.57347000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5465,7 +5513,7 @@
         <v>0.56618000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5473,7 +5521,7 @@
         <v>0.56489999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -5481,7 +5529,7 @@
         <v>0.56618000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -5493,7 +5541,7 @@
         <v>0.47383999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5501,7 +5549,7 @@
         <v>0.46977000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -5509,7 +5557,7 @@
         <v>0.44077</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -5521,7 +5569,7 @@
         <v>0.50119000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -5529,7 +5577,7 @@
         <v>0.41348000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -5541,7 +5589,7 @@
         <v>0.49658000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -5549,7 +5597,7 @@
         <v>0.49658000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -5561,7 +5609,7 @@
         <v>0.47960000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -5569,7 +5617,7 @@
         <v>0.47960000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -5577,7 +5625,7 @@
         <v>0.47815000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -5585,7 +5633,7 @@
         <v>0.42636000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -5597,7 +5645,7 @@
         <v>0.51910000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -5605,7 +5653,7 @@
         <v>0.51861999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -5613,7 +5661,7 @@
         <v>0.51910000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -5621,7 +5669,7 @@
         <v>0.51822000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -5633,7 +5681,7 @@
         <v>0.43720999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -5641,7 +5689,7 @@
         <v>0.42781999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -5653,7 +5701,7 @@
         <v>0.47666999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -5661,7 +5709,7 @@
         <v>0.41425000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -5669,7 +5717,7 @@
         <v>0.47589999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -5677,7 +5725,7 @@
         <v>0.47666999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -5689,7 +5737,7 @@
         <v>0.53641000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -5697,7 +5745,7 @@
         <v>0.48127999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -5705,7 +5753,7 @@
         <v>0.53117999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -5713,7 +5761,7 @@
         <v>0.53641000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -5725,7 +5773,7 @@
         <v>0.47381000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -5733,7 +5781,7 @@
         <v>0.47099000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -5741,7 +5789,7 @@
         <v>0.44855</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -5753,7 +5801,7 @@
         <v>0.49945000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -5769,9 +5817,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8B5A3-CE5B-4A8C-9C85-AF312DF32E51}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5779,7 +5827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5791,7 +5839,7 @@
         <v>0.54093000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5799,7 +5847,7 @@
         <v>0.50585000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -5811,7 +5859,7 @@
         <v>0.53190999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -5819,7 +5867,7 @@
         <v>0.53190999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5827,7 +5875,7 @@
         <v>0.52966000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5835,7 +5883,7 @@
         <v>0.52924000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5847,7 +5895,7 @@
         <v>0.52542999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -5855,7 +5903,7 @@
         <v>0.52542999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5863,7 +5911,7 @@
         <v>0.52431000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5875,7 +5923,7 @@
         <v>0.50183</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -5883,7 +5931,7 @@
         <v>0.46189000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -5891,7 +5939,7 @@
         <v>0.49682999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -5903,7 +5951,7 @@
         <v>0.50183</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -5911,7 +5959,7 @@
         <v>0.47619</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -5919,7 +5967,7 @@
         <v>0.49084</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -5931,7 +5979,7 @@
         <v>0.50344999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -5939,7 +5987,7 @@
         <v>0.50344999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -5951,7 +5999,7 @@
         <v>0.50726000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -5959,7 +6007,7 @@
         <v>0.48048000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -5971,7 +6019,7 @@
         <v>0.53417000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -5979,7 +6027,7 @@
         <v>0.53036000000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -5987,7 +6035,7 @@
         <v>0.53417000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -5999,7 +6047,7 @@
         <v>0.51853000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -6007,7 +6055,7 @@
         <v>0.51726000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -6015,7 +6063,7 @@
         <v>0.49556</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -6027,7 +6075,7 @@
         <v>0.58291999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -6035,7 +6083,7 @@
         <v>0.56559000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -6043,7 +6091,7 @@
         <v>0.58291999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -6055,7 +6103,7 @@
         <v>0.49569999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -6063,7 +6111,7 @@
         <v>0.47089999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -6071,7 +6119,7 @@
         <v>0.49569999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -6083,7 +6131,7 @@
         <v>0.55686000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -6091,7 +6139,7 @@
         <v>0.55318999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -6107,9 +6155,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B796E0-256A-4A27-9A69-9963FBE3B123}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -6117,7 +6165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6129,7 +6177,7 @@
         <v>0.68383000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -6137,7 +6185,7 @@
         <v>0.68383000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -6145,7 +6193,7 @@
         <v>0.67630999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -6153,7 +6201,7 @@
         <v>0.68213999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -6165,7 +6213,7 @@
         <v>0.66883000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -6173,7 +6221,7 @@
         <v>0.66861000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -6181,7 +6229,7 @@
         <v>0.66883000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -6193,7 +6241,7 @@
         <v>0.65583000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -6201,7 +6249,7 @@
         <v>0.65583000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -6213,7 +6261,7 @@
         <v>0.56933</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -6221,7 +6269,7 @@
         <v>0.56760999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -6229,7 +6277,7 @@
         <v>0.56933</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -6241,7 +6289,7 @@
         <v>0.56138999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -6249,7 +6297,7 @@
         <v>0.54483000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -6257,7 +6305,7 @@
         <v>0.54805999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -6265,7 +6313,7 @@
         <v>0.56138999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -6277,7 +6325,7 @@
         <v>0.56906000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -6285,7 +6333,7 @@
         <v>0.56521999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -6293,7 +6341,7 @@
         <v>0.56906000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -6305,7 +6353,7 @@
         <v>0.60592000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -6313,7 +6361,7 @@
         <v>0.60592000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -6321,7 +6369,7 @@
         <v>0.60472000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -6329,7 +6377,7 @@
         <v>0.59699999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -6341,7 +6389,7 @@
         <v>0.75566999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -6349,7 +6397,7 @@
         <v>0.75217000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -6357,7 +6405,7 @@
         <v>0.75566999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6369,7 +6417,7 @@
         <v>0.55693999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -6377,7 +6425,7 @@
         <v>0.54117000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -6385,7 +6433,7 @@
         <v>0.55393999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -6393,7 +6441,7 @@
         <v>0.55693999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -6405,7 +6453,7 @@
         <v>0.72055999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -6413,7 +6461,7 @@
         <v>0.71494000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -6421,7 +6469,7 @@
         <v>0.72055999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -6429,7 +6477,7 @@
         <v>0.70011000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -6441,7 +6489,7 @@
         <v>0.55967</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -6449,7 +6497,7 @@
         <v>0.55967</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -6457,7 +6505,7 @@
         <v>0.54881000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -6465,7 +6513,7 @@
         <v>0.55528</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -6477,7 +6525,7 @@
         <v>0.71682999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -6485,7 +6533,7 @@
         <v>0.71150000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -6493,7 +6541,7 @@
         <v>0.71011000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>29</v>
       </c>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\Documents\GitHub\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DBCB9-04DB-4355-885C-89C865A11373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33A9E76-9617-4155-8E90-383325483487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,7 +308,49 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3717,31 +3759,31 @@
         <v>0.74376999999999993</v>
       </c>
       <c r="N14" s="2">
-        <f>AVERAGE(N3:N13)</f>
+        <f t="shared" ref="N14:T14" si="1">AVERAGE(N3:N13)</f>
         <v>0.7803154126486137</v>
       </c>
       <c r="O14" s="2">
-        <f>AVERAGE(O3:O13)</f>
+        <f t="shared" si="1"/>
         <v>0.93570909090909093</v>
       </c>
       <c r="P14" s="3">
-        <f>AVERAGE(P3:P13)</f>
+        <f t="shared" si="1"/>
         <v>0.78261144820912876</v>
       </c>
       <c r="Q14" s="3">
-        <f>AVERAGE(Q3:Q13)</f>
+        <f t="shared" si="1"/>
         <v>0.95763636363636384</v>
       </c>
       <c r="R14" s="3">
-        <f>AVERAGE(R3:R13)</f>
+        <f t="shared" si="1"/>
         <v>0.78293058512378733</v>
       </c>
       <c r="S14" s="3">
-        <f>AVERAGE(S3:S13)</f>
+        <f t="shared" si="1"/>
         <v>0.96839090909090897</v>
       </c>
       <c r="T14" s="3">
-        <f>AVERAGE(T3:T13)</f>
+        <f t="shared" si="1"/>
         <v>0.75045194010767158</v>
       </c>
     </row>
@@ -3757,62 +3799,62 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" t="str">
-        <f t="shared" ref="B19:B28" si="1">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
+        <f t="shared" ref="B19:B28" si="2">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
         <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242]</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846]</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774]</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444]</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069]</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
       </c>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048]</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956]</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477]</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025]</v>
       </c>
     </row>
@@ -3932,14 +3974,19 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="N1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:N14 P3:P14 R3:R14 T3:T14 S3:S13">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>B3=MAX($B3:$N3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3:S13 B3:N14 P3:P14 R3:R14 T3:T14">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>B3=MAX($B3:$N3)</formula>
+  <conditionalFormatting sqref="O3:O14 Q3:Q14 S3:S14">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>O3=MAX($O3,$Q3,$S3)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C470EF79-42E7-4D48-A66A-4AAF67C5AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE3BD24-8ADA-4F0F-8BBC-747C264DE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="45">
   <si>
     <t>Arrhy</t>
   </si>
@@ -213,16 +213,22 @@
     <t>Log Gamma</t>
   </si>
   <si>
-    <t>LogNorm</t>
-  </si>
-  <si>
     <t>BoxPlot</t>
   </si>
   <si>
     <t>Log Gamma R^2</t>
   </si>
   <si>
-    <t>Log Norm R^2</t>
+    <t xml:space="preserve">Gamma </t>
+  </si>
+  <si>
+    <t>Log SkewNorm</t>
+  </si>
+  <si>
+    <t>LogSkewNorm</t>
+  </si>
+  <si>
+    <t>Log SkewNorm R^2</t>
   </si>
 </sst>
 </file>
@@ -266,7 +272,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -294,13 +300,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -308,19 +323,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -620,34 +745,46 @@
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="13" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="16.5703125" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="15.85546875" customWidth="1"/>
-    <col min="17" max="17" width="24.140625" customWidth="1"/>
-    <col min="19" max="19" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="24.140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="7"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
     </row>
     <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -699,16 +836,16 @@
         <v>38</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -1394,260 +1531,334 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <f>AVERAGE(B3:B13)</f>
         <v>0.76385363636363646</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <f t="shared" ref="C14:M14" si="0">AVERAGE(C3:C13)</f>
         <v>0.74898363636363641</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f t="shared" si="0"/>
         <v>0.73779636363636358</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f t="shared" si="0"/>
         <v>0.71585272727272731</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <f t="shared" si="0"/>
         <v>0.7080581818181817</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f t="shared" si="0"/>
         <v>0.68091363636363633</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f t="shared" si="0"/>
         <v>0.70191727272727278</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f t="shared" si="0"/>
         <v>0.70524545454545462</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <f t="shared" si="0"/>
         <v>0.63380727272727266</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <f t="shared" si="0"/>
         <v>0.75610909090909084</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <f t="shared" si="0"/>
         <v>0.69330909090909087</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <f t="shared" si="0"/>
         <v>0.74376999999999993</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="8">
         <f t="shared" ref="N14:T14" si="1">AVERAGE(N3:N13)</f>
         <v>0.7803154126486137</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <f t="shared" si="1"/>
         <v>0.93570909090909093</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <f t="shared" si="1"/>
         <v>0.78261144820912876</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <f t="shared" si="1"/>
         <v>0.95763636363636384</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="9">
         <f t="shared" si="1"/>
         <v>0.78293058512378733</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S14" s="9">
         <f t="shared" si="1"/>
         <v>0.96839090909090897</v>
       </c>
-      <c r="T14" s="10">
+      <c r="T14" s="9">
         <f t="shared" si="1"/>
         <v>0.75045194010767158</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
-        <f>_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B3:N3),"]")</f>
-        <v>[0.752,0.75008,0.74421,0.74339,0.74111,0.73452,0.72669,0.74176,0.66101,0.72286,0.73154,0.73385,0.761081489734203]</v>
-      </c>
-      <c r="M18" t="str">
+        <f>_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B3:N3,P3,R3,T3),"]")</f>
+        <v>[0.752,0.75008,0.74421,0.74339,0.74111,0.73452,0.72669,0.74176,0.66101,0.72286,0.73154,0.73385,0.761081489734203,0.760872592710488,0.759877844978513,0.755670062072258]</v>
+      </c>
+      <c r="Q18" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,A3:A13)</f>
         <v>Arrhythmia','Parkinson','Shuttle','WBC','SpamBase','WPBC','HeartDisease','Glass','Hepatitis','Pima','PenDigits</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
-        <f t="shared" ref="B19:B28" si="2">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4),"]")</f>
-        <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242]</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+        <f t="shared" ref="B19:B28" si="2">_xlfn.CONCAT("[",_xlfn.TEXTJOIN(",",TRUE,B4:N4,P4,R4,T4),"]")</f>
+        <v>[0.65235,0.64399,0.61196,0.60728,0.58312,0.55315,0.52608,0.66993,0.58673,0.60218,0.59198,0.64966,0.738166099773242,0.74000850340136,0.739158163265306,0.631164965986394]</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="2"/>
-        <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846]</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.81762,0.72785,0.78208,0.76608,0.78992,0.84754,0.789,0.316,0.69192,0.71585,0.79885,0.63969,0.820153846153846,0.845653846153846,0.845653846153846,0.819884615384615]</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" t="str">
         <f t="shared" si="2"/>
-        <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774]</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.99718,0.99718,0.99671,0.9939,0.98028,0.96526,0.96737,0.99484,0.64789,0.99718,0.9939,0.99437,0.998591549295774,0.993661971830986,0.996244131455399,0.929577464788732]</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" t="str">
         <f t="shared" si="2"/>
-        <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444]</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.57347,0.56618,0.47384,0.50119,0.49658,0.4796,0.5191,0.43721,0.47667,0.53641,0.47381,0.49945,0.650009471053444,0.650563127162793,0.650166261751645,0.587739886234271]</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f t="shared" si="2"/>
-        <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069]</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.5409,0.53191,0.52543,0.50183,0.50183,0.50345,0.50726,0.53417,0.51853,0.58292,0.4957,0.55686,0.531562632098069,0.532196702832182,0.53170353670565,0.52973087219952]</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" t="str">
         <f t="shared" si="2"/>
-        <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666]</v>
+        <v>[0.68383,0.66883,0.65583,0.56933,0.56139,0.56906,0.60592,0.75567,0.55694,0.72056,0.55967,0.71683,0.700166666666666,0.699027777777777,0.700527777777777,0.657861111111111]</v>
       </c>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f t="shared" si="2"/>
-        <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048]</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.8748,0.8832,0.86667,0.86504,0.83957,0.77886,0.72927,0.85799,0.74201,0.90352,0.80379,0.89539,0.880487804878048,0.877777777777777,0.876151761517615,0.862059620596206]</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f t="shared" si="2"/>
-        <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956]</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.78588,0.74856,0.80367,0.73823,0.72331,0.73823,0.74971,0.70953,0.71183,0.82893,0.60276,0.82721,0.784730195177956,0.785878300803674,0.788174512055109,0.784156142365097]</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" t="str">
         <f t="shared" si="2"/>
-        <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477]</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.73224,0.72944,0.68955,0.62131,0.60922,0.57004,0.63637,0.76081,0.55621,0.72888,0.61728,0.70121,0.735914179104477,0.735671641791044,0.737190298507462,0.730988805970149]</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="str">
         <f t="shared" si="2"/>
-        <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025]</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+        <v>[0.99212,0.9916,0.96581,0.9668,0.96231,0.75034,0.96432,0.97979,0.82214,0.97791,0.95712,0.96695,0.982605605199025,0.987413688058489,0.987388302193338,0.966137794476035]</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" t="str">
         <f>_xlfn.TEXTJOIN("','",TRUE,B2:N2)</f>
         <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="2">
         <v>0.97450000000000003</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" s="3">
+        <v>0.99539999999999995</v>
+      </c>
+      <c r="D34" s="12">
+        <v>0.99490000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1</v>
       </c>
       <c r="B35" s="2">
         <v>0.85409999999999997</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="D35" s="12">
+        <v>0.96919999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>2</v>
       </c>
       <c r="B36" s="2">
         <v>0.72499999999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" s="3">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="D36" s="12">
+        <v>0.99250000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="2">
         <v>0.98670000000000002</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" s="3">
+        <v>0.9395</v>
+      </c>
+      <c r="D37" s="12">
+        <v>0.93279999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
       <c r="B38" s="2">
         <v>0.92220000000000002</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="3">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="D38" s="12">
+        <v>0.83940000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39" s="2">
         <v>0.98599999999999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="3">
+        <v>0.99229999999999996</v>
+      </c>
+      <c r="D39" s="12">
+        <v>0.98950000000000005</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2">
         <v>0.99390000000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="3">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="D40" s="12">
+        <v>0.99309999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>7</v>
       </c>
       <c r="B41" s="2">
         <v>0.93869999999999998</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="3">
+        <v>0.97550000000000003</v>
+      </c>
+      <c r="D41" s="12">
+        <v>0.98719999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="2">
         <v>0.93610000000000004</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="D42" s="12">
+        <v>0.96450000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="2">
         <v>0.997</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="C43" s="3">
+        <v>0.99080000000000001</v>
+      </c>
+      <c r="D43" s="12">
+        <v>0.99060000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="14">
         <v>0.97860000000000003</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" s="15">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="D44" s="16">
+        <v>0.99860000000000004</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -1655,24 +1866,42 @@
         <f>AVERAGE(B34:B44)</f>
         <v>0.93570909090909093</v>
       </c>
+      <c r="C45" s="3">
+        <f>AVERAGE(C34:C44)</f>
+        <v>0.95763636363636384</v>
+      </c>
+      <c r="D45" s="12">
+        <f>AVERAGE(D34:D44)</f>
+        <v>0.96839090909090897</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N1:T1"/>
   </mergeCells>
+  <conditionalFormatting sqref="C34:D34 C35:C44">
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C34=MAX($O34,$Q34,$S34)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>D34=MAX($B34:$N34,$P34,$R34,$T34)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="17" priority="5">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O14 Q3:Q14 S3:S14">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>O3=MAX($O3,$Q3,$S3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S13 B3:N14 P3:P14 R3:R14 T3:T14">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3618,10 +3847,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814B012A-D937-47C4-8AC9-6A6E5FDF72BE}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3629,7 +3861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3637,7 +3869,7 @@
         <v>0.74761</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3645,7 +3877,7 @@
         <v>0.75158000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3657,7 +3889,7 @@
         <v>0.75205</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3665,7 +3897,7 @@
         <v>0.74997999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3673,7 +3905,7 @@
         <v>0.74456999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3681,7 +3913,7 @@
         <v>0.74836999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3693,7 +3925,7 @@
         <v>0.75007999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3701,7 +3933,7 @@
         <v>0.75007999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3709,7 +3941,7 @@
         <v>0.71584000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -3717,7 +3949,7 @@
         <v>0.72428000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3729,7 +3961,7 @@
         <v>0.74421000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -3737,7 +3969,7 @@
         <v>0.74414999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -3745,15 +3977,27 @@
         <v>0.71930000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
       <c r="B15">
         <v>0.73812</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -3764,32 +4008,80 @@
         <f>MAX(B14:B17)</f>
         <v>0.74339</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.97450000000000003</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.99539999999999995</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.99490000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17">
         <v>0.74319999999999997</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.85409999999999997</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.96919999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18">
         <v>0.71847000000000005</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.99250000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
       <c r="B19">
         <v>0.73836000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.98670000000000002</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.9395</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.93279999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -3800,24 +4092,60 @@
         <f>MAX(B18:B21)</f>
         <v>0.74111000000000005</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.83940000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="B21">
         <v>0.74097000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.99229999999999996</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.98950000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
       <c r="B22">
         <v>0.71986000000000006</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.99309999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -3828,16 +4156,40 @@
         <f>MAX(B22:B24)</f>
         <v>0.73451999999999995</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.93869999999999998</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.97550000000000003</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.98719999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
       <c r="B24">
         <v>0.73451999999999995</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.93610000000000004</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.96550000000000002</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.96450000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -3848,24 +4200,60 @@
         <f>MAX(B25:B27)</f>
         <v>0.72668999999999995</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.997</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0.99080000000000001</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.99060000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <v>0.72275999999999996</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.97860000000000003</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.99860000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27">
         <v>0.72668999999999995</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0.93570909090909093</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0.95763636363636384</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0.96839090909090897</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3877,7 +4265,7 @@
         <v>0.74175999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -3885,7 +4273,7 @@
         <v>0.74175999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -3897,7 +4285,7 @@
         <v>0.66100999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -3905,7 +4293,7 @@
         <v>0.66100999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE3BD24-8ADA-4F0F-8BBC-747C264DE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996EB329-481B-418A-A3F1-D6F445CEF07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,7 +315,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -326,114 +326,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <b/>
@@ -762,29 +670,29 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
     </row>
     <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1690,7 +1598,7 @@
         <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -1714,7 +1622,7 @@
       <c r="C34" s="3">
         <v>0.99539999999999995</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="3">
         <v>0.99490000000000001</v>
       </c>
     </row>
@@ -1728,7 +1636,7 @@
       <c r="C35" s="3">
         <v>0.96550000000000002</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="3">
         <v>0.96919999999999995</v>
       </c>
     </row>
@@ -1742,7 +1650,7 @@
       <c r="C36" s="3">
         <v>0.99239999999999995</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="3">
         <v>0.99250000000000005</v>
       </c>
     </row>
@@ -1756,7 +1664,7 @@
       <c r="C37" s="3">
         <v>0.9395</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="3">
         <v>0.93279999999999996</v>
       </c>
     </row>
@@ -1770,7 +1678,7 @@
       <c r="C38" s="3">
         <v>0.72509999999999997</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="3">
         <v>0.83940000000000003</v>
       </c>
     </row>
@@ -1784,7 +1692,7 @@
       <c r="C39" s="3">
         <v>0.99229999999999996</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="3">
         <v>0.98950000000000005</v>
       </c>
     </row>
@@ -1798,7 +1706,7 @@
       <c r="C40" s="3">
         <v>0.99390000000000001</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="3">
         <v>0.99309999999999998</v>
       </c>
     </row>
@@ -1812,7 +1720,7 @@
       <c r="C41" s="3">
         <v>0.97550000000000003</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="3">
         <v>0.98719999999999997</v>
       </c>
     </row>
@@ -1826,7 +1734,7 @@
       <c r="C42" s="3">
         <v>0.96550000000000002</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="3">
         <v>0.96450000000000002</v>
       </c>
     </row>
@@ -1840,21 +1748,21 @@
       <c r="C43" s="3">
         <v>0.99080000000000001</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="3">
         <v>0.99060000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="11">
         <v>0.97860000000000003</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="12">
         <v>0.99809999999999999</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="12">
         <v>0.99860000000000004</v>
       </c>
     </row>
@@ -1870,7 +1778,7 @@
         <f>AVERAGE(C34:C44)</f>
         <v>0.95763636363636384</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="3">
         <f>AVERAGE(D34:D44)</f>
         <v>0.96839090909090897</v>
       </c>
@@ -1881,27 +1789,27 @@
     <mergeCell ref="N1:T1"/>
   </mergeCells>
   <conditionalFormatting sqref="C34:D34 C35:C44">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>C34=MAX($O34,$Q34,$S34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D34">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>D34=MAX($B34:$N34,$P34,$R34,$T34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="17" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O14 Q3:Q14 S3:S14">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>O3=MAX($O3,$Q3,$S3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S13 B3:N14 P3:P14 R3:R14 T3:T14">
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ResultsNew.xlsx
+++ b/ResultsNew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996EB329-481B-418A-A3F1-D6F445CEF07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47077020-8C71-456D-BADB-6336B3420712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="45">
   <si>
     <t>Arrhy</t>
   </si>
@@ -225,10 +225,10 @@
     <t>Log SkewNorm</t>
   </si>
   <si>
-    <t>LogSkewNorm</t>
+    <t>Log SkewNorm R^2</t>
   </si>
   <si>
-    <t>Log SkewNorm R^2</t>
+    <t>Q-Q Plot R^2</t>
   </si>
 </sst>
 </file>
@@ -341,7 +341,49 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -652,20 +694,20 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.140625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="9.140625" hidden="1" customWidth="1"/>
     <col min="11" max="13" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" customWidth="1"/>
     <col min="17" max="17" width="24.140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="18.42578125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="2.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -747,10 +789,10 @@
         <v>40</v>
       </c>
       <c r="R2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>39</v>
@@ -1598,6 +1640,11 @@
         <v>KNN','KNNW','LOF','SimplifiedLOF','LoOP','LDOF','ODIN','FastABOD','KDEOS','LDF','INFLO','COF','Gamma</v>
       </c>
     </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>11</v>
@@ -1789,28 +1836,33 @@
     <mergeCell ref="N1:T1"/>
   </mergeCells>
   <conditionalFormatting sqref="C34:D34 C35:C44">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>C34=MAX($O34,$Q34,$S34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D34">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>D34=MAX($B34:$N34,$P34,$R34,$T34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>B3=MAX($B3:$N3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O14 Q3:Q14 S3:S14">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>O3=MAX($O3,$Q3,$S3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S13 B3:N14 P3:P14 R3:R14 T3:T14">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>B3=MAX($B3:$N3,$P3,$R3,$T3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:D45">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>B34=MAX($B34,$C34,$D34)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
